--- a/watermarking_model/results/evals/detection_metrics.xlsx
+++ b/watermarking_model/results/evals/detection_metrics.xlsx
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -1289,19 +1289,19 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.981155</v>
+        <v>0.993638</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.003333</v>
+        <v>0.007889</v>
       </c>
       <c r="O18" t="n">
-        <v>0.000883</v>
+        <v>0.003565</v>
       </c>
       <c r="P18" t="n">
-        <v>0.027774</v>
+        <v>0.019358</v>
       </c>
       <c r="Q18" t="n">
         <v>13</v>
@@ -1310,7 +1310,7 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.00614</v>
+        <v>0.008389000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -1350,19 +1350,19 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.981155</v>
+        <v>0.993638</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.006667</v>
+        <v>0.010778</v>
       </c>
       <c r="O19" t="n">
-        <v>0.000883</v>
+        <v>0.004591</v>
       </c>
       <c r="P19" t="n">
-        <v>0.027774</v>
+        <v>0.021644</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -1371,7 +1371,7 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.007368</v>
+        <v>0.011152</v>
       </c>
     </row>
     <row r="20">
@@ -1381,58 +1381,58 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C20" t="n">
-        <v>0.799167</v>
+        <v>0.795042</v>
       </c>
       <c r="D20" t="n">
-        <v>0.122948</v>
+        <v>0.123665</v>
       </c>
       <c r="E20" t="n">
-        <v>0.008694</v>
+        <v>0.005049</v>
       </c>
       <c r="F20" t="n">
-        <v>0.772961</v>
+        <v>0.780522</v>
       </c>
       <c r="G20" t="n">
-        <v>0.807039</v>
+        <v>0.800312</v>
       </c>
       <c r="H20" t="n">
-        <v>0.96905</v>
+        <v>0.951219</v>
       </c>
       <c r="I20" t="n">
-        <v>0.946448</v>
+        <v>0.9371660000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9774659999999999</v>
+        <v>0.9592889999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.573333</v>
+        <v>0.590333</v>
       </c>
       <c r="L20" t="n">
-        <v>0.470823</v>
+        <v>0.533415</v>
       </c>
       <c r="M20" t="n">
-        <v>0.607669</v>
+        <v>0.612318</v>
       </c>
       <c r="N20" t="n">
-        <v>0.006667</v>
+        <v>0.013222</v>
       </c>
       <c r="O20" t="n">
-        <v>0.000883</v>
+        <v>0.005663</v>
       </c>
       <c r="P20" t="n">
-        <v>0.027774</v>
+        <v>0.023884</v>
       </c>
       <c r="Q20" t="n">
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>0.61193</v>
+        <v>0.594216</v>
       </c>
       <c r="S20" t="n">
-        <v>0.010877</v>
+        <v>0.014061</v>
       </c>
     </row>
     <row r="21">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -1472,19 +1472,19 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.981155</v>
+        <v>0.993638</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.003333</v>
+        <v>0.009556</v>
       </c>
       <c r="O21" t="n">
-        <v>0.000883</v>
+        <v>0.004591</v>
       </c>
       <c r="P21" t="n">
-        <v>0.027774</v>
+        <v>0.021644</v>
       </c>
       <c r="Q21" t="n">
         <v>13</v>
@@ -1493,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.008947</v>
+        <v>0.010109</v>
       </c>
     </row>
     <row r="22">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -1533,19 +1533,19 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.981155</v>
+        <v>0.993638</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.006667</v>
+        <v>0.009889</v>
       </c>
       <c r="O22" t="n">
-        <v>0.000883</v>
+        <v>0.004591</v>
       </c>
       <c r="P22" t="n">
-        <v>0.027774</v>
+        <v>0.021644</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
@@ -1554,7 +1554,7 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.010175</v>
+        <v>0.010616</v>
       </c>
     </row>
     <row r="23">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1594,19 +1594,19 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.981155</v>
+        <v>0.993638</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.007111</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>0.002596</v>
       </c>
       <c r="P23" t="n">
-        <v>0.018845</v>
+        <v>0.017015</v>
       </c>
       <c r="Q23" t="n">
         <v>13</v>
@@ -1615,7 +1615,7 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.001404</v>
+        <v>0.007611</v>
       </c>
     </row>
     <row r="24">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1655,19 +1655,19 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.981155</v>
+        <v>0.993638</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.003333</v>
+        <v>0.007889</v>
       </c>
       <c r="O24" t="n">
-        <v>0.000883</v>
+        <v>0.003565</v>
       </c>
       <c r="P24" t="n">
-        <v>0.027774</v>
+        <v>0.019358</v>
       </c>
       <c r="Q24" t="n">
         <v>13</v>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.00614</v>
+        <v>0.008389000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1716,19 +1716,19 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.981155</v>
+        <v>0.993638</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.01</v>
+        <v>0.013111</v>
       </c>
       <c r="O25" t="n">
-        <v>0.002747</v>
+        <v>0.006771</v>
       </c>
       <c r="P25" t="n">
-        <v>0.035722</v>
+        <v>0.026087</v>
       </c>
       <c r="Q25" t="n">
         <v>13</v>
@@ -1737,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.012807</v>
+        <v>0.013888</v>
       </c>
     </row>
     <row r="26">
@@ -1747,58 +1747,58 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C26" t="n">
-        <v>0.996458</v>
+        <v>0.99825</v>
       </c>
       <c r="D26" t="n">
-        <v>0.031795</v>
+        <v>0.019216</v>
       </c>
       <c r="E26" t="n">
-        <v>0.002248</v>
+        <v>0.000785</v>
       </c>
       <c r="F26" t="n">
-        <v>0.992469</v>
+        <v>0.9969</v>
       </c>
       <c r="G26" t="n">
-        <v>1.001281</v>
+        <v>0.9999749999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9982</v>
+        <v>0.999281</v>
       </c>
       <c r="I26" t="n">
-        <v>0.995762</v>
+        <v>0.998354</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0.993333</v>
+        <v>0.9977780000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>0.972226</v>
+        <v>0.9906199999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>0.999117</v>
+        <v>0.999706</v>
       </c>
       <c r="N26" t="n">
-        <v>0.006667</v>
+        <v>0.010111</v>
       </c>
       <c r="O26" t="n">
-        <v>0.002747</v>
+        <v>0.004591</v>
       </c>
       <c r="P26" t="n">
-        <v>0.035722</v>
+        <v>0.021644</v>
       </c>
       <c r="Q26" t="n">
         <v>13</v>
       </c>
       <c r="R26" t="n">
-        <v>0.993333</v>
+        <v>0.9977780000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>0.015789</v>
+        <v>0.011115</v>
       </c>
     </row>
     <row r="27">
@@ -1808,58 +1808,58 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="C27" t="n">
-        <v>0.555</v>
+        <v>0.530896</v>
       </c>
       <c r="D27" t="n">
-        <v>0.131937</v>
+        <v>0.125151</v>
       </c>
       <c r="E27" t="n">
-        <v>0.009329</v>
+        <v>0.005109</v>
       </c>
       <c r="F27" t="n">
-        <v>0.535152</v>
+        <v>0.5200900000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.571723</v>
+        <v>0.540118</v>
       </c>
       <c r="H27" t="n">
-        <v>0.612567</v>
+        <v>0.5629459999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.555246</v>
+        <v>0.527917</v>
       </c>
       <c r="J27" t="n">
-        <v>0.666431</v>
+        <v>0.593959</v>
       </c>
       <c r="K27" t="n">
-        <v>0.036667</v>
+        <v>0.018889</v>
       </c>
       <c r="L27" t="n">
-        <v>0.017056</v>
+        <v>0.011477</v>
       </c>
       <c r="M27" t="n">
-        <v>0.07047100000000001</v>
+        <v>0.03463</v>
       </c>
       <c r="N27" t="n">
-        <v>0.013333</v>
+        <v>0.006111</v>
       </c>
       <c r="O27" t="n">
-        <v>0.002747</v>
+        <v>0.001702</v>
       </c>
       <c r="P27" t="n">
-        <v>0.035722</v>
+        <v>0.014596</v>
       </c>
       <c r="Q27" t="n">
         <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>0.054912</v>
+        <v>0.0202</v>
       </c>
       <c r="S27" t="n">
-        <v>0.016842</v>
+        <v>0.006894</v>
       </c>
     </row>
     <row r="29">
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -4166,19 +4166,19 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.006667</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.001178</v>
       </c>
       <c r="P18" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.036793</v>
       </c>
       <c r="Q18" t="n">
         <v>13</v>
@@ -4187,7 +4187,7 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.006834</v>
       </c>
     </row>
     <row r="19">
@@ -4197,7 +4197,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -4227,19 +4227,19 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.013333</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.003664</v>
       </c>
       <c r="P19" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.047307</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -4248,7 +4248,7 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.013501</v>
       </c>
     </row>
     <row r="20">
@@ -4258,58 +4258,58 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C20" t="n">
         <v>0.8125</v>
       </c>
       <c r="D20" t="n">
-        <v>0.123718</v>
+        <v>0.123311</v>
       </c>
       <c r="E20" t="n">
-        <v>0.017496</v>
+        <v>0.010068</v>
       </c>
       <c r="F20" t="n">
-        <v>0.778208</v>
+        <v>0.792767</v>
       </c>
       <c r="G20" t="n">
-        <v>0.846792</v>
+        <v>0.832233</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9698</v>
+        <v>0.945444</v>
       </c>
       <c r="I20" t="n">
-        <v>0.935995</v>
+        <v>0.918303</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9936</v>
+        <v>0.968297</v>
       </c>
       <c r="K20" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="L20" t="n">
-        <v>0.481504</v>
+        <v>0.581043</v>
       </c>
       <c r="M20" t="n">
-        <v>0.741372</v>
+        <v>0.730967</v>
       </c>
       <c r="N20" t="n">
-        <v>0.02</v>
+        <v>0.026667</v>
       </c>
       <c r="O20" t="n">
-        <v>0.003539</v>
+        <v>0.010418</v>
       </c>
       <c r="P20" t="n">
-        <v>0.104954</v>
+        <v>0.066554</v>
       </c>
       <c r="Q20" t="n">
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>0.653684</v>
+        <v>0.663019</v>
       </c>
       <c r="S20" t="n">
-        <v>0.024211</v>
+        <v>0.028176</v>
       </c>
     </row>
     <row r="21">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -4349,19 +4349,19 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.006667</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.001178</v>
       </c>
       <c r="P21" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.036793</v>
       </c>
       <c r="Q21" t="n">
         <v>13</v>
@@ -4370,7 +4370,7 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.00717</v>
       </c>
     </row>
     <row r="22">
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -4410,19 +4410,19 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.006667</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.001178</v>
       </c>
       <c r="P22" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.036793</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
@@ -4431,7 +4431,7 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.007338</v>
       </c>
     </row>
     <row r="23">
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -4471,19 +4471,19 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.013333</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>0.003664</v>
       </c>
       <c r="P23" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.047307</v>
       </c>
       <c r="Q23" t="n">
         <v>13</v>
@@ -4492,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.013501</v>
       </c>
     </row>
     <row r="24">
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -4532,19 +4532,19 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.006667</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>0.001178</v>
       </c>
       <c r="P24" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.036793</v>
       </c>
       <c r="Q24" t="n">
         <v>13</v>
@@ -4553,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.006834</v>
       </c>
     </row>
     <row r="25">
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -4593,19 +4593,19 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.013333</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.003664</v>
       </c>
       <c r="P25" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.047307</v>
       </c>
       <c r="Q25" t="n">
         <v>13</v>
@@ -4614,7 +4614,7 @@
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>0.014004</v>
       </c>
     </row>
     <row r="26">
@@ -4624,58 +4624,58 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C26" t="n">
-        <v>0.99125</v>
+        <v>0.99625</v>
       </c>
       <c r="D26" t="n">
-        <v>0.061872</v>
+        <v>0.036371</v>
       </c>
       <c r="E26" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.00297</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9741</v>
+        <v>0.990429</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0084</v>
+        <v>1.002071</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9946</v>
+        <v>0.997844</v>
       </c>
       <c r="I26" t="n">
-        <v>0.982</v>
+        <v>0.992667</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0.98</v>
+        <v>0.993333</v>
       </c>
       <c r="L26" t="n">
-        <v>0.895046</v>
+        <v>0.963207</v>
       </c>
       <c r="M26" t="n">
-        <v>0.996461</v>
+        <v>0.998822</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>0.013333</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>0.003664</v>
       </c>
       <c r="P26" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.047307</v>
       </c>
       <c r="Q26" t="n">
         <v>13</v>
       </c>
       <c r="R26" t="n">
-        <v>0.98</v>
+        <v>0.993333</v>
       </c>
       <c r="S26" t="n">
-        <v>0.008421</v>
+        <v>0.014004</v>
       </c>
     </row>
     <row r="27">
@@ -4685,58 +4685,58 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C27" t="n">
-        <v>0.54875</v>
+        <v>0.5325</v>
       </c>
       <c r="D27" t="n">
-        <v>0.128949</v>
+        <v>0.118479</v>
       </c>
       <c r="E27" t="n">
-        <v>0.018236</v>
+        <v>0.009674</v>
       </c>
       <c r="F27" t="n">
-        <v>0.513008</v>
+        <v>0.51354</v>
       </c>
       <c r="G27" t="n">
-        <v>0.584492</v>
+        <v>0.55146</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6112</v>
+        <v>0.579956</v>
       </c>
       <c r="I27" t="n">
-        <v>0.498575</v>
+        <v>0.513798</v>
       </c>
       <c r="J27" t="n">
-        <v>0.72201</v>
+        <v>0.6444260000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.02</v>
+        <v>0.006667</v>
       </c>
       <c r="L27" t="n">
-        <v>0.003539</v>
+        <v>0.001178</v>
       </c>
       <c r="M27" t="n">
-        <v>0.104954</v>
+        <v>0.036793</v>
       </c>
       <c r="N27" t="n">
-        <v>0.02</v>
+        <v>0.013333</v>
       </c>
       <c r="O27" t="n">
-        <v>0.003539</v>
+        <v>0.003664</v>
       </c>
       <c r="P27" t="n">
-        <v>0.104954</v>
+        <v>0.047307</v>
       </c>
       <c r="Q27" t="n">
         <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>0.045263</v>
+        <v>0.008512</v>
       </c>
       <c r="S27" t="n">
-        <v>0.02</v>
+        <v>0.014172</v>
       </c>
     </row>
     <row r="29">
@@ -7013,7 +7013,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -7043,19 +7043,19 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.000883</v>
       </c>
       <c r="P18" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.027774</v>
       </c>
       <c r="Q18" t="n">
         <v>13</v>
@@ -7064,7 +7064,7 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.004211</v>
+        <v>0.005629</v>
       </c>
     </row>
     <row r="19">
@@ -7074,7 +7074,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -7104,19 +7104,19 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="O19" t="n">
-        <v>0.003539</v>
+        <v>0.005114</v>
       </c>
       <c r="P19" t="n">
-        <v>0.104954</v>
+        <v>0.043166</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -7125,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.02</v>
+        <v>0.015252</v>
       </c>
     </row>
     <row r="20">
@@ -7135,58 +7135,58 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8225</v>
+        <v>0.815625</v>
       </c>
       <c r="D20" t="n">
-        <v>0.093097</v>
+        <v>0.102717</v>
       </c>
       <c r="E20" t="n">
-        <v>0.013166</v>
+        <v>0.007263</v>
       </c>
       <c r="F20" t="n">
-        <v>0.796695</v>
+        <v>0.801389</v>
       </c>
       <c r="G20" t="n">
-        <v>0.848305</v>
+        <v>0.829861</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9779870000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9746</v>
+        <v>0.9665820000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9986</v>
+        <v>0.987726</v>
       </c>
       <c r="K20" t="n">
-        <v>0.66</v>
+        <v>0.655</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5215379999999999</v>
+        <v>0.5867560000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.775631</v>
+        <v>0.717402</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.000883</v>
       </c>
       <c r="P20" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.027774</v>
       </c>
       <c r="Q20" t="n">
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7063160000000001</v>
+        <v>0.659403</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004211</v>
+        <v>0.005503</v>
       </c>
     </row>
     <row r="21">
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -7226,19 +7226,19 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.002747</v>
       </c>
       <c r="P21" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.035722</v>
       </c>
       <c r="Q21" t="n">
         <v>13</v>
@@ -7247,7 +7247,7 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.012632</v>
+        <v>0.010755</v>
       </c>
     </row>
     <row r="22">
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -7287,19 +7287,19 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="O22" t="n">
-        <v>0.003539</v>
+        <v>0.005114</v>
       </c>
       <c r="P22" t="n">
-        <v>0.104954</v>
+        <v>0.043166</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
@@ -7308,7 +7308,7 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.024211</v>
+        <v>0.015503</v>
       </c>
     </row>
     <row r="23">
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -7348,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
@@ -7360,7 +7360,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.018845</v>
       </c>
       <c r="Q23" t="n">
         <v>13</v>
@@ -7369,7 +7369,7 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.000629</v>
       </c>
     </row>
     <row r="24">
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -7409,19 +7409,19 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>0.000883</v>
       </c>
       <c r="P24" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.027774</v>
       </c>
       <c r="Q24" t="n">
         <v>13</v>
@@ -7430,7 +7430,7 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.004211</v>
+        <v>0.005629</v>
       </c>
     </row>
     <row r="25">
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -7470,19 +7470,19 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O25" t="n">
-        <v>0.003539</v>
+        <v>0.002747</v>
       </c>
       <c r="P25" t="n">
-        <v>0.104954</v>
+        <v>0.035722</v>
       </c>
       <c r="Q25" t="n">
         <v>13</v>
@@ -7491,7 +7491,7 @@
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.02</v>
+        <v>0.010755</v>
       </c>
     </row>
     <row r="26">
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -7531,19 +7531,19 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>0.000883</v>
       </c>
       <c r="P26" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.027774</v>
       </c>
       <c r="Q26" t="n">
         <v>13</v>
@@ -7552,7 +7552,7 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.012632</v>
+        <v>0.006635</v>
       </c>
     </row>
     <row r="27">
@@ -7562,58 +7562,58 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5675</v>
+        <v>0.537188</v>
       </c>
       <c r="D27" t="n">
-        <v>0.133535</v>
+        <v>0.129033</v>
       </c>
       <c r="E27" t="n">
-        <v>0.018885</v>
+        <v>0.009124</v>
       </c>
       <c r="F27" t="n">
-        <v>0.530487</v>
+        <v>0.519305</v>
       </c>
       <c r="G27" t="n">
-        <v>0.604513</v>
+        <v>0.55507</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6258</v>
+        <v>0.56525</v>
       </c>
       <c r="I27" t="n">
-        <v>0.519755</v>
+        <v>0.51131</v>
       </c>
       <c r="J27" t="n">
-        <v>0.726805</v>
+        <v>0.620413</v>
       </c>
       <c r="K27" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="L27" t="n">
-        <v>0.020615</v>
+        <v>0.01382</v>
       </c>
       <c r="M27" t="n">
-        <v>0.162171</v>
+        <v>0.06389400000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="O27" t="n">
-        <v>0.003539</v>
+        <v>0.000883</v>
       </c>
       <c r="P27" t="n">
-        <v>0.104954</v>
+        <v>0.027774</v>
       </c>
       <c r="Q27" t="n">
         <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>0.072632</v>
+        <v>0.030881</v>
       </c>
       <c r="S27" t="n">
-        <v>0.024211</v>
+        <v>0.006006</v>
       </c>
     </row>
     <row r="29">
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -9920,19 +9920,19 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="O18" t="n">
-        <v>0.001767</v>
+        <v>0.004089</v>
       </c>
       <c r="P18" t="n">
-        <v>0.054486</v>
+        <v>0.034681</v>
       </c>
       <c r="Q18" t="n">
         <v>13</v>
@@ -9941,7 +9941,7 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.014211</v>
+        <v>0.012704</v>
       </c>
     </row>
     <row r="19">
@@ -9951,7 +9951,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -9981,19 +9981,19 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.000706</v>
       </c>
       <c r="P19" t="n">
-        <v>0.036993</v>
+        <v>0.022306</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -10002,7 +10002,7 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.002105</v>
+        <v>0.004704</v>
       </c>
     </row>
     <row r="20">
@@ -10012,58 +10012,58 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7625</v>
+        <v>0.757</v>
       </c>
       <c r="D20" t="n">
-        <v>0.130256</v>
+        <v>0.131654</v>
       </c>
       <c r="E20" t="n">
-        <v>0.013026</v>
+        <v>0.008326999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.73697</v>
+        <v>0.74068</v>
       </c>
       <c r="G20" t="n">
-        <v>0.78803</v>
+        <v>0.77332</v>
       </c>
       <c r="H20" t="n">
-        <v>0.94795</v>
+        <v>0.9302240000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.92055</v>
+        <v>0.91047</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9717</v>
+        <v>0.948041</v>
       </c>
       <c r="K20" t="n">
-        <v>0.44</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
-        <v>0.34672</v>
+        <v>0.395392</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5377189999999999</v>
+        <v>0.51794</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.002197</v>
       </c>
       <c r="P20" t="n">
-        <v>0.036993</v>
+        <v>0.028695</v>
       </c>
       <c r="Q20" t="n">
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>0.475789</v>
+        <v>0.460226</v>
       </c>
       <c r="S20" t="n">
-        <v>0.004211</v>
+        <v>0.008503</v>
       </c>
     </row>
     <row r="21">
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -10103,19 +10103,19 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="O21" t="n">
-        <v>0.001767</v>
+        <v>0.004089</v>
       </c>
       <c r="P21" t="n">
-        <v>0.054486</v>
+        <v>0.034681</v>
       </c>
       <c r="Q21" t="n">
         <v>13</v>
@@ -10124,7 +10124,7 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.014211</v>
+        <v>0.012403</v>
       </c>
     </row>
     <row r="22">
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -10164,19 +10164,19 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.002197</v>
       </c>
       <c r="P22" t="n">
-        <v>0.036993</v>
+        <v>0.028695</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
@@ -10185,7 +10185,7 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.006316</v>
+        <v>0.009006</v>
       </c>
     </row>
     <row r="23">
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -10225,19 +10225,19 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>0.002197</v>
       </c>
       <c r="P23" t="n">
-        <v>0.036993</v>
+        <v>0.028695</v>
       </c>
       <c r="Q23" t="n">
         <v>13</v>
@@ -10246,7 +10246,7 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.004211</v>
+        <v>0.008704</v>
       </c>
     </row>
     <row r="24">
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -10286,19 +10286,19 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="O24" t="n">
-        <v>0.001767</v>
+        <v>0.004089</v>
       </c>
       <c r="P24" t="n">
-        <v>0.054486</v>
+        <v>0.034681</v>
       </c>
       <c r="Q24" t="n">
         <v>13</v>
@@ -10307,7 +10307,7 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.014211</v>
+        <v>0.012704</v>
       </c>
     </row>
     <row r="25">
@@ -10317,7 +10317,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -10347,19 +10347,19 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="O25" t="n">
-        <v>0.001767</v>
+        <v>0.006239</v>
       </c>
       <c r="P25" t="n">
-        <v>0.054486</v>
+        <v>0.04041</v>
       </c>
       <c r="Q25" t="n">
         <v>13</v>
@@ -10368,7 +10368,7 @@
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.018421</v>
+        <v>0.016906</v>
       </c>
     </row>
     <row r="26">
@@ -10378,22 +10378,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C26" t="n">
-        <v>0.998125</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.010715</v>
+        <v>0.009585</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001072</v>
+        <v>0.000606</v>
       </c>
       <c r="F26" t="n">
-        <v>0.996025</v>
+        <v>0.997312</v>
       </c>
       <c r="G26" t="n">
-        <v>1.000225</v>
+        <v>0.999688</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -10408,19 +10408,19 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="O26" t="n">
-        <v>0.005502</v>
+        <v>0.004089</v>
       </c>
       <c r="P26" t="n">
-        <v>0.070012</v>
+        <v>0.034681</v>
       </c>
       <c r="Q26" t="n">
         <v>13</v>
@@ -10429,7 +10429,7 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.026316</v>
+        <v>0.012704</v>
       </c>
     </row>
     <row r="27">
@@ -10439,40 +10439,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C27" t="n">
-        <v>0.54875</v>
+        <v>0.523</v>
       </c>
       <c r="D27" t="n">
-        <v>0.133422</v>
+        <v>0.126009</v>
       </c>
       <c r="E27" t="n">
-        <v>0.013342</v>
+        <v>0.00797</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5226</v>
+        <v>0.5073800000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5749</v>
+        <v>0.53862</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6007</v>
+        <v>0.543632</v>
       </c>
       <c r="I27" t="n">
-        <v>0.522331</v>
+        <v>0.488739</v>
       </c>
       <c r="J27" t="n">
-        <v>0.675755</v>
+        <v>0.594282</v>
       </c>
       <c r="K27" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="L27" t="n">
-        <v>0.010255</v>
+        <v>0.008572</v>
       </c>
       <c r="M27" t="n">
-        <v>0.084519</v>
+        <v>0.045956</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -10481,16 +10481,16 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.036993</v>
+        <v>0.015133</v>
       </c>
       <c r="Q27" t="n">
         <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>0.046842</v>
+        <v>0.021208</v>
       </c>
       <c r="S27" t="n">
-        <v>0.006316</v>
+        <v>0.000503</v>
       </c>
     </row>
     <row r="29">
@@ -12039,10 +12039,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006</v>
+        <v>0.009332999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>0.01</v>
@@ -12051,7 +12051,7 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>0.210526</v>
+        <v>0.025157</v>
       </c>
     </row>
     <row r="4">
@@ -15892,7 +15892,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -15922,19 +15922,19 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>0.006667</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>0.001178</v>
       </c>
       <c r="R42" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.036793</v>
       </c>
       <c r="S42" t="n">
         <v>13</v>
@@ -15943,7 +15943,7 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.006834</v>
       </c>
     </row>
     <row r="43">
@@ -15963,7 +15963,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -15993,19 +15993,19 @@
         <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>0.013333</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>0.003664</v>
       </c>
       <c r="R43" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.047307</v>
       </c>
       <c r="S43" t="n">
         <v>13</v>
@@ -16014,7 +16014,7 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>0.013501</v>
       </c>
     </row>
     <row r="44">
@@ -16034,58 +16034,58 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E44" t="n">
         <v>0.8125</v>
       </c>
       <c r="F44" t="n">
-        <v>0.123718</v>
+        <v>0.123311</v>
       </c>
       <c r="G44" t="n">
-        <v>0.017496</v>
+        <v>0.010068</v>
       </c>
       <c r="H44" t="n">
-        <v>0.778208</v>
+        <v>0.792767</v>
       </c>
       <c r="I44" t="n">
-        <v>0.846792</v>
+        <v>0.832233</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9698</v>
+        <v>0.945444</v>
       </c>
       <c r="K44" t="n">
-        <v>0.935995</v>
+        <v>0.918303</v>
       </c>
       <c r="L44" t="n">
-        <v>0.9936</v>
+        <v>0.968297</v>
       </c>
       <c r="M44" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="N44" t="n">
-        <v>0.481504</v>
+        <v>0.581043</v>
       </c>
       <c r="O44" t="n">
-        <v>0.741372</v>
+        <v>0.730967</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02</v>
+        <v>0.026667</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.003539</v>
+        <v>0.010418</v>
       </c>
       <c r="R44" t="n">
-        <v>0.104954</v>
+        <v>0.066554</v>
       </c>
       <c r="S44" t="n">
         <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>0.653684</v>
+        <v>0.663019</v>
       </c>
       <c r="U44" t="n">
-        <v>0.024211</v>
+        <v>0.028176</v>
       </c>
     </row>
     <row r="45">
@@ -16105,7 +16105,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -16135,19 +16135,19 @@
         <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>0.006667</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>0.001178</v>
       </c>
       <c r="R45" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.036793</v>
       </c>
       <c r="S45" t="n">
         <v>13</v>
@@ -16156,7 +16156,7 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>0.00717</v>
       </c>
     </row>
     <row r="46">
@@ -16176,7 +16176,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -16206,19 +16206,19 @@
         <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>0.006667</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.001178</v>
       </c>
       <c r="R46" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.036793</v>
       </c>
       <c r="S46" t="n">
         <v>13</v>
@@ -16227,7 +16227,7 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.007338</v>
       </c>
     </row>
     <row r="47">
@@ -16247,7 +16247,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -16277,19 +16277,19 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>0.013333</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>0.003664</v>
       </c>
       <c r="R47" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.047307</v>
       </c>
       <c r="S47" t="n">
         <v>13</v>
@@ -16298,7 +16298,7 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>0.013501</v>
       </c>
     </row>
     <row r="48">
@@ -16318,7 +16318,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -16348,19 +16348,19 @@
         <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>0.006667</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>0.001178</v>
       </c>
       <c r="R48" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.036793</v>
       </c>
       <c r="S48" t="n">
         <v>13</v>
@@ -16369,7 +16369,7 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.006834</v>
       </c>
     </row>
     <row r="49">
@@ -16389,7 +16389,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -16419,19 +16419,19 @@
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>0.928652</v>
+        <v>0.97503</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>0.013333</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>0.003664</v>
       </c>
       <c r="R49" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.047307</v>
       </c>
       <c r="S49" t="n">
         <v>13</v>
@@ -16440,7 +16440,7 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.014004</v>
       </c>
     </row>
     <row r="50">
@@ -16460,58 +16460,58 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E50" t="n">
-        <v>0.99125</v>
+        <v>0.99625</v>
       </c>
       <c r="F50" t="n">
-        <v>0.061872</v>
+        <v>0.036371</v>
       </c>
       <c r="G50" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.00297</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9741</v>
+        <v>0.990429</v>
       </c>
       <c r="I50" t="n">
-        <v>1.0084</v>
+        <v>1.002071</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9946</v>
+        <v>0.997844</v>
       </c>
       <c r="K50" t="n">
-        <v>0.982</v>
+        <v>0.992667</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.98</v>
+        <v>0.993333</v>
       </c>
       <c r="N50" t="n">
-        <v>0.895046</v>
+        <v>0.963207</v>
       </c>
       <c r="O50" t="n">
-        <v>0.996461</v>
+        <v>0.998822</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>0.013333</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>0.003664</v>
       </c>
       <c r="R50" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.047307</v>
       </c>
       <c r="S50" t="n">
         <v>13</v>
       </c>
       <c r="T50" t="n">
-        <v>0.98</v>
+        <v>0.993333</v>
       </c>
       <c r="U50" t="n">
-        <v>0.008421</v>
+        <v>0.014004</v>
       </c>
     </row>
     <row r="51">
@@ -16531,58 +16531,58 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E51" t="n">
-        <v>0.54875</v>
+        <v>0.5325</v>
       </c>
       <c r="F51" t="n">
-        <v>0.128949</v>
+        <v>0.118479</v>
       </c>
       <c r="G51" t="n">
-        <v>0.018236</v>
+        <v>0.009674</v>
       </c>
       <c r="H51" t="n">
-        <v>0.513008</v>
+        <v>0.51354</v>
       </c>
       <c r="I51" t="n">
-        <v>0.584492</v>
+        <v>0.55146</v>
       </c>
       <c r="J51" t="n">
-        <v>0.6112</v>
+        <v>0.579956</v>
       </c>
       <c r="K51" t="n">
-        <v>0.498575</v>
+        <v>0.513798</v>
       </c>
       <c r="L51" t="n">
-        <v>0.72201</v>
+        <v>0.6444260000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>0.02</v>
+        <v>0.006667</v>
       </c>
       <c r="N51" t="n">
-        <v>0.003539</v>
+        <v>0.001178</v>
       </c>
       <c r="O51" t="n">
-        <v>0.104954</v>
+        <v>0.036793</v>
       </c>
       <c r="P51" t="n">
-        <v>0.02</v>
+        <v>0.013333</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.003539</v>
+        <v>0.003664</v>
       </c>
       <c r="R51" t="n">
-        <v>0.104954</v>
+        <v>0.047307</v>
       </c>
       <c r="S51" t="n">
         <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>0.045263</v>
+        <v>0.008512</v>
       </c>
       <c r="U51" t="n">
-        <v>0.02</v>
+        <v>0.014172</v>
       </c>
     </row>
     <row r="52">
@@ -16602,7 +16602,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -16632,19 +16632,19 @@
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>0.000883</v>
       </c>
       <c r="R52" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.027774</v>
       </c>
       <c r="S52" t="n">
         <v>13</v>
@@ -16653,7 +16653,7 @@
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>0.004211</v>
+        <v>0.005629</v>
       </c>
     </row>
     <row r="53">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -16703,19 +16703,19 @@
         <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.003539</v>
+        <v>0.005114</v>
       </c>
       <c r="R53" t="n">
-        <v>0.104954</v>
+        <v>0.043166</v>
       </c>
       <c r="S53" t="n">
         <v>13</v>
@@ -16724,7 +16724,7 @@
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>0.02</v>
+        <v>0.015252</v>
       </c>
     </row>
     <row r="54">
@@ -16744,58 +16744,58 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8225</v>
+        <v>0.815625</v>
       </c>
       <c r="F54" t="n">
-        <v>0.093097</v>
+        <v>0.102717</v>
       </c>
       <c r="G54" t="n">
-        <v>0.013166</v>
+        <v>0.007263</v>
       </c>
       <c r="H54" t="n">
-        <v>0.796695</v>
+        <v>0.801389</v>
       </c>
       <c r="I54" t="n">
-        <v>0.848305</v>
+        <v>0.829861</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9779870000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9746</v>
+        <v>0.9665820000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>0.9986</v>
+        <v>0.987726</v>
       </c>
       <c r="M54" t="n">
-        <v>0.66</v>
+        <v>0.655</v>
       </c>
       <c r="N54" t="n">
-        <v>0.5215379999999999</v>
+        <v>0.5867560000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>0.775631</v>
+        <v>0.717402</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>0.000883</v>
       </c>
       <c r="R54" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.027774</v>
       </c>
       <c r="S54" t="n">
         <v>13</v>
       </c>
       <c r="T54" t="n">
-        <v>0.7063160000000001</v>
+        <v>0.659403</v>
       </c>
       <c r="U54" t="n">
-        <v>0.004211</v>
+        <v>0.005503</v>
       </c>
     </row>
     <row r="55">
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -16845,19 +16845,19 @@
         <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>0.002747</v>
       </c>
       <c r="R55" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.035722</v>
       </c>
       <c r="S55" t="n">
         <v>13</v>
@@ -16866,7 +16866,7 @@
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>0.012632</v>
+        <v>0.010755</v>
       </c>
     </row>
     <row r="56">
@@ -16886,7 +16886,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -16916,19 +16916,19 @@
         <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
       </c>
       <c r="P56" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.003539</v>
+        <v>0.005114</v>
       </c>
       <c r="R56" t="n">
-        <v>0.104954</v>
+        <v>0.043166</v>
       </c>
       <c r="S56" t="n">
         <v>13</v>
@@ -16937,7 +16937,7 @@
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>0.024211</v>
+        <v>0.015503</v>
       </c>
     </row>
     <row r="57">
@@ -16957,7 +16957,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -16987,7 +16987,7 @@
         <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
@@ -16999,7 +16999,7 @@
         <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.018845</v>
       </c>
       <c r="S57" t="n">
         <v>13</v>
@@ -17008,7 +17008,7 @@
         <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>0.000629</v>
       </c>
     </row>
     <row r="58">
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -17058,19 +17058,19 @@
         <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>0.000883</v>
       </c>
       <c r="R58" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.027774</v>
       </c>
       <c r="S58" t="n">
         <v>13</v>
@@ -17079,7 +17079,7 @@
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>0.004211</v>
+        <v>0.005629</v>
       </c>
     </row>
     <row r="59">
@@ -17099,7 +17099,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -17129,19 +17129,19 @@
         <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="O59" t="n">
         <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.003539</v>
+        <v>0.002747</v>
       </c>
       <c r="R59" t="n">
-        <v>0.104954</v>
+        <v>0.035722</v>
       </c>
       <c r="S59" t="n">
         <v>13</v>
@@ -17150,7 +17150,7 @@
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>0.02</v>
+        <v>0.010755</v>
       </c>
     </row>
     <row r="60">
@@ -17170,7 +17170,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -17200,19 +17200,19 @@
         <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>0.928652</v>
+        <v>0.981155</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>0.000883</v>
       </c>
       <c r="R60" t="n">
-        <v>0.07134799999999999</v>
+        <v>0.027774</v>
       </c>
       <c r="S60" t="n">
         <v>13</v>
@@ -17221,7 +17221,7 @@
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>0.012632</v>
+        <v>0.006635</v>
       </c>
     </row>
     <row r="61">
@@ -17241,58 +17241,58 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E61" t="n">
-        <v>0.5675</v>
+        <v>0.537188</v>
       </c>
       <c r="F61" t="n">
-        <v>0.133535</v>
+        <v>0.129033</v>
       </c>
       <c r="G61" t="n">
-        <v>0.018885</v>
+        <v>0.009124</v>
       </c>
       <c r="H61" t="n">
-        <v>0.530487</v>
+        <v>0.519305</v>
       </c>
       <c r="I61" t="n">
-        <v>0.604513</v>
+        <v>0.55507</v>
       </c>
       <c r="J61" t="n">
-        <v>0.6258</v>
+        <v>0.56525</v>
       </c>
       <c r="K61" t="n">
-        <v>0.519755</v>
+        <v>0.51131</v>
       </c>
       <c r="L61" t="n">
-        <v>0.726805</v>
+        <v>0.620413</v>
       </c>
       <c r="M61" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="N61" t="n">
-        <v>0.020615</v>
+        <v>0.01382</v>
       </c>
       <c r="O61" t="n">
-        <v>0.162171</v>
+        <v>0.06389400000000001</v>
       </c>
       <c r="P61" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.003539</v>
+        <v>0.000883</v>
       </c>
       <c r="R61" t="n">
-        <v>0.104954</v>
+        <v>0.027774</v>
       </c>
       <c r="S61" t="n">
         <v>13</v>
       </c>
       <c r="T61" t="n">
-        <v>0.072632</v>
+        <v>0.030881</v>
       </c>
       <c r="U61" t="n">
-        <v>0.024211</v>
+        <v>0.006006</v>
       </c>
     </row>
     <row r="62">
@@ -17312,7 +17312,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -17342,19 +17342,19 @@
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.001767</v>
+        <v>0.004089</v>
       </c>
       <c r="R62" t="n">
-        <v>0.054486</v>
+        <v>0.034681</v>
       </c>
       <c r="S62" t="n">
         <v>13</v>
@@ -17363,7 +17363,7 @@
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>0.014211</v>
+        <v>0.012704</v>
       </c>
     </row>
     <row r="63">
@@ -17383,7 +17383,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -17413,19 +17413,19 @@
         <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>0.000706</v>
       </c>
       <c r="R63" t="n">
-        <v>0.036993</v>
+        <v>0.022306</v>
       </c>
       <c r="S63" t="n">
         <v>13</v>
@@ -17434,7 +17434,7 @@
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>0.002105</v>
+        <v>0.004704</v>
       </c>
     </row>
     <row r="64">
@@ -17454,58 +17454,58 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7625</v>
+        <v>0.757</v>
       </c>
       <c r="F64" t="n">
-        <v>0.130256</v>
+        <v>0.131654</v>
       </c>
       <c r="G64" t="n">
-        <v>0.013026</v>
+        <v>0.008326999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>0.73697</v>
+        <v>0.74068</v>
       </c>
       <c r="I64" t="n">
-        <v>0.78803</v>
+        <v>0.77332</v>
       </c>
       <c r="J64" t="n">
-        <v>0.94795</v>
+        <v>0.9302240000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>0.92055</v>
+        <v>0.91047</v>
       </c>
       <c r="L64" t="n">
-        <v>0.9717</v>
+        <v>0.948041</v>
       </c>
       <c r="M64" t="n">
-        <v>0.44</v>
+        <v>0.456</v>
       </c>
       <c r="N64" t="n">
-        <v>0.34672</v>
+        <v>0.395392</v>
       </c>
       <c r="O64" t="n">
-        <v>0.5377189999999999</v>
+        <v>0.51794</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>0.002197</v>
       </c>
       <c r="R64" t="n">
-        <v>0.036993</v>
+        <v>0.028695</v>
       </c>
       <c r="S64" t="n">
         <v>13</v>
       </c>
       <c r="T64" t="n">
-        <v>0.475789</v>
+        <v>0.460226</v>
       </c>
       <c r="U64" t="n">
-        <v>0.004211</v>
+        <v>0.008503</v>
       </c>
     </row>
     <row r="65">
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -17555,19 +17555,19 @@
         <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.001767</v>
+        <v>0.004089</v>
       </c>
       <c r="R65" t="n">
-        <v>0.054486</v>
+        <v>0.034681</v>
       </c>
       <c r="S65" t="n">
         <v>13</v>
@@ -17576,7 +17576,7 @@
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>0.014211</v>
+        <v>0.012403</v>
       </c>
     </row>
     <row r="66">
@@ -17596,7 +17596,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -17626,19 +17626,19 @@
         <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="O66" t="n">
         <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>0.002197</v>
       </c>
       <c r="R66" t="n">
-        <v>0.036993</v>
+        <v>0.028695</v>
       </c>
       <c r="S66" t="n">
         <v>13</v>
@@ -17647,7 +17647,7 @@
         <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>0.006316</v>
+        <v>0.009006</v>
       </c>
     </row>
     <row r="67">
@@ -17667,7 +17667,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
@@ -17697,19 +17697,19 @@
         <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>0.002197</v>
       </c>
       <c r="R67" t="n">
-        <v>0.036993</v>
+        <v>0.028695</v>
       </c>
       <c r="S67" t="n">
         <v>13</v>
@@ -17718,7 +17718,7 @@
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0.004211</v>
+        <v>0.008704</v>
       </c>
     </row>
     <row r="68">
@@ -17738,7 +17738,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -17768,19 +17768,19 @@
         <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.001767</v>
+        <v>0.004089</v>
       </c>
       <c r="R68" t="n">
-        <v>0.054486</v>
+        <v>0.034681</v>
       </c>
       <c r="S68" t="n">
         <v>13</v>
@@ -17789,7 +17789,7 @@
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>0.014211</v>
+        <v>0.012704</v>
       </c>
     </row>
     <row r="69">
@@ -17809,7 +17809,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -17839,19 +17839,19 @@
         <v>1</v>
       </c>
       <c r="N69" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="O69" t="n">
         <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.001767</v>
+        <v>0.006239</v>
       </c>
       <c r="R69" t="n">
-        <v>0.054486</v>
+        <v>0.04041</v>
       </c>
       <c r="S69" t="n">
         <v>13</v>
@@ -17860,7 +17860,7 @@
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>0.018421</v>
+        <v>0.016906</v>
       </c>
     </row>
     <row r="70">
@@ -17880,22 +17880,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E70" t="n">
-        <v>0.998125</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>0.010715</v>
+        <v>0.009585</v>
       </c>
       <c r="G70" t="n">
-        <v>0.001072</v>
+        <v>0.000606</v>
       </c>
       <c r="H70" t="n">
-        <v>0.996025</v>
+        <v>0.997312</v>
       </c>
       <c r="I70" t="n">
-        <v>1.000225</v>
+        <v>0.999688</v>
       </c>
       <c r="J70" t="n">
         <v>1</v>
@@ -17910,19 +17910,19 @@
         <v>1</v>
       </c>
       <c r="N70" t="n">
-        <v>0.9630069999999999</v>
+        <v>0.984867</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.005502</v>
+        <v>0.004089</v>
       </c>
       <c r="R70" t="n">
-        <v>0.070012</v>
+        <v>0.034681</v>
       </c>
       <c r="S70" t="n">
         <v>13</v>
@@ -17931,7 +17931,7 @@
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>0.026316</v>
+        <v>0.012704</v>
       </c>
     </row>
     <row r="71">
@@ -17951,40 +17951,40 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E71" t="n">
-        <v>0.54875</v>
+        <v>0.523</v>
       </c>
       <c r="F71" t="n">
-        <v>0.133422</v>
+        <v>0.126009</v>
       </c>
       <c r="G71" t="n">
-        <v>0.013342</v>
+        <v>0.00797</v>
       </c>
       <c r="H71" t="n">
-        <v>0.5226</v>
+        <v>0.5073800000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5749</v>
+        <v>0.53862</v>
       </c>
       <c r="J71" t="n">
-        <v>0.6007</v>
+        <v>0.543632</v>
       </c>
       <c r="K71" t="n">
-        <v>0.522331</v>
+        <v>0.488739</v>
       </c>
       <c r="L71" t="n">
-        <v>0.675755</v>
+        <v>0.594282</v>
       </c>
       <c r="M71" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="N71" t="n">
-        <v>0.010255</v>
+        <v>0.008572</v>
       </c>
       <c r="O71" t="n">
-        <v>0.084519</v>
+        <v>0.045956</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -17993,16 +17993,16 @@
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.036993</v>
+        <v>0.015133</v>
       </c>
       <c r="S71" t="n">
         <v>13</v>
       </c>
       <c r="T71" t="n">
-        <v>0.046842</v>
+        <v>0.021208</v>
       </c>
       <c r="U71" t="n">
-        <v>0.006316</v>
+        <v>0.000503</v>
       </c>
     </row>
     <row r="72">

--- a/watermarking_model/results/evals/detection_metrics.xlsx
+++ b/watermarking_model/results/evals/detection_metrics.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -1289,19 +1289,19 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.993638</v>
+        <v>0.995973</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.007889</v>
+        <v>0.008777999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.003565</v>
+        <v>0.004992</v>
       </c>
       <c r="P18" t="n">
-        <v>0.019358</v>
+        <v>0.017906</v>
       </c>
       <c r="Q18" t="n">
         <v>13</v>
@@ -1310,7 +1310,7 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.008389000000000001</v>
+        <v>0.009344</v>
       </c>
     </row>
     <row r="19">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -1350,19 +1350,19 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.993638</v>
+        <v>0.995973</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.010778</v>
+        <v>0.0115</v>
       </c>
       <c r="O19" t="n">
-        <v>0.004591</v>
+        <v>0.006478</v>
       </c>
       <c r="P19" t="n">
-        <v>0.021644</v>
+        <v>0.020614</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -1371,7 +1371,7 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.011152</v>
+        <v>0.012065</v>
       </c>
     </row>
     <row r="20">
@@ -1381,58 +1381,58 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="C20" t="n">
-        <v>0.795042</v>
+        <v>0.796337</v>
       </c>
       <c r="D20" t="n">
-        <v>0.123665</v>
+        <v>0.12525</v>
       </c>
       <c r="E20" t="n">
-        <v>0.005049</v>
+        <v>0.004064</v>
       </c>
       <c r="F20" t="n">
-        <v>0.780522</v>
+        <v>0.783285</v>
       </c>
       <c r="G20" t="n">
-        <v>0.800312</v>
+        <v>0.799215</v>
       </c>
       <c r="H20" t="n">
-        <v>0.951219</v>
+        <v>0.9526559999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9371660000000001</v>
+        <v>0.940667</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9592889999999999</v>
+        <v>0.957543</v>
       </c>
       <c r="K20" t="n">
-        <v>0.590333</v>
+        <v>0.589556</v>
       </c>
       <c r="L20" t="n">
-        <v>0.533415</v>
+        <v>0.540944</v>
       </c>
       <c r="M20" t="n">
-        <v>0.612318</v>
+        <v>0.603735</v>
       </c>
       <c r="N20" t="n">
-        <v>0.013222</v>
+        <v>0.010889</v>
       </c>
       <c r="O20" t="n">
-        <v>0.005663</v>
+        <v>0.005728</v>
       </c>
       <c r="P20" t="n">
-        <v>0.023884</v>
+        <v>0.019268</v>
       </c>
       <c r="Q20" t="n">
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>0.594216</v>
+        <v>0.594232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.014061</v>
+        <v>0.011668</v>
       </c>
     </row>
     <row r="21">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -1472,19 +1472,19 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.993638</v>
+        <v>0.995973</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.009556</v>
+        <v>0.008222</v>
       </c>
       <c r="O21" t="n">
-        <v>0.004591</v>
+        <v>0.004273</v>
       </c>
       <c r="P21" t="n">
-        <v>0.021644</v>
+        <v>0.016528</v>
       </c>
       <c r="Q21" t="n">
         <v>13</v>
@@ -1493,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.010109</v>
+        <v>0.008933999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -1533,19 +1533,19 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.993638</v>
+        <v>0.995973</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.009889</v>
+        <v>0.010167</v>
       </c>
       <c r="O22" t="n">
-        <v>0.004591</v>
+        <v>0.005728</v>
       </c>
       <c r="P22" t="n">
-        <v>0.021644</v>
+        <v>0.019268</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
@@ -1554,7 +1554,7 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.010616</v>
+        <v>0.010961</v>
       </c>
     </row>
     <row r="23">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1594,19 +1594,19 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.993638</v>
+        <v>0.995973</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.007111</v>
+        <v>0.005444</v>
       </c>
       <c r="O23" t="n">
-        <v>0.002596</v>
+        <v>0.00225</v>
       </c>
       <c r="P23" t="n">
-        <v>0.017015</v>
+        <v>0.012261</v>
       </c>
       <c r="Q23" t="n">
         <v>13</v>
@@ -1615,7 +1615,7 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.007611</v>
+        <v>0.006083</v>
       </c>
     </row>
     <row r="24">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1655,19 +1655,19 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.993638</v>
+        <v>0.995973</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.007889</v>
+        <v>0.008777999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.003565</v>
+        <v>0.004992</v>
       </c>
       <c r="P24" t="n">
-        <v>0.019358</v>
+        <v>0.017906</v>
       </c>
       <c r="Q24" t="n">
         <v>13</v>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.008389000000000001</v>
+        <v>0.009344</v>
       </c>
     </row>
     <row r="25">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1716,19 +1716,19 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.993638</v>
+        <v>0.995973</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.013111</v>
+        <v>0.011556</v>
       </c>
       <c r="O25" t="n">
-        <v>0.006771</v>
+        <v>0.00724</v>
       </c>
       <c r="P25" t="n">
-        <v>0.026087</v>
+        <v>0.021948</v>
       </c>
       <c r="Q25" t="n">
         <v>13</v>
@@ -1737,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.013888</v>
+        <v>0.012357</v>
       </c>
     </row>
     <row r="26">
@@ -1747,58 +1747,58 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="C26" t="n">
-        <v>0.99825</v>
+        <v>0.998885</v>
       </c>
       <c r="D26" t="n">
-        <v>0.019216</v>
+        <v>0.015415</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000785</v>
+        <v>0.0005</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9969</v>
+        <v>0.997967</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9999749999999999</v>
+        <v>0.999928</v>
       </c>
       <c r="H26" t="n">
-        <v>0.999281</v>
+        <v>0.999571</v>
       </c>
       <c r="I26" t="n">
-        <v>0.998354</v>
+        <v>0.998956</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9977780000000001</v>
+        <v>0.998667</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9906199999999999</v>
+        <v>0.994062</v>
       </c>
       <c r="M26" t="n">
-        <v>0.999706</v>
+        <v>0.999814</v>
       </c>
       <c r="N26" t="n">
-        <v>0.010111</v>
+        <v>0.008944000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>0.004591</v>
+        <v>0.004273</v>
       </c>
       <c r="P26" t="n">
-        <v>0.021644</v>
+        <v>0.016528</v>
       </c>
       <c r="Q26" t="n">
         <v>13</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9977780000000001</v>
+        <v>0.998667</v>
       </c>
       <c r="S26" t="n">
-        <v>0.011115</v>
+        <v>0.010021</v>
       </c>
     </row>
     <row r="27">
@@ -1808,58 +1808,58 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="C27" t="n">
-        <v>0.530896</v>
+        <v>0.52774</v>
       </c>
       <c r="D27" t="n">
-        <v>0.125151</v>
+        <v>0.124637</v>
       </c>
       <c r="E27" t="n">
-        <v>0.005109</v>
+        <v>0.004044</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5200900000000001</v>
+        <v>0.519509</v>
       </c>
       <c r="G27" t="n">
-        <v>0.540118</v>
+        <v>0.5353599999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5629459999999999</v>
+        <v>0.562635</v>
       </c>
       <c r="I27" t="n">
-        <v>0.527917</v>
+        <v>0.537809</v>
       </c>
       <c r="J27" t="n">
-        <v>0.593959</v>
+        <v>0.5896439999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.018889</v>
+        <v>0.020667</v>
       </c>
       <c r="L27" t="n">
-        <v>0.011477</v>
+        <v>0.013669</v>
       </c>
       <c r="M27" t="n">
-        <v>0.03463</v>
+        <v>0.032294</v>
       </c>
       <c r="N27" t="n">
-        <v>0.006111</v>
+        <v>0.007333</v>
       </c>
       <c r="O27" t="n">
-        <v>0.001702</v>
+        <v>0.002898</v>
       </c>
       <c r="P27" t="n">
-        <v>0.014596</v>
+        <v>0.01371</v>
       </c>
       <c r="Q27" t="n">
         <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0202</v>
+        <v>0.022136</v>
       </c>
       <c r="S27" t="n">
-        <v>0.006894</v>
+        <v>0.008296</v>
       </c>
     </row>
     <row r="29">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -2717,19 +2717,19 @@
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.995221</v>
+        <v>0.996173</v>
       </c>
       <c r="M44" t="n">
         <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>0.005</v>
+        <v>0.0075</v>
       </c>
       <c r="O44" t="n">
-        <v>0.001946</v>
+        <v>0.003395</v>
       </c>
       <c r="P44" t="n">
-        <v>0.012785</v>
+        <v>0.014378</v>
       </c>
       <c r="Q44" t="n">
         <v>9</v>
@@ -2738,7 +2738,7 @@
         <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.006461</v>
+        <v>0.008359999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -2778,19 +2778,19 @@
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.995221</v>
+        <v>0.996173</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>0.0125</v>
+        <v>0.012083</v>
       </c>
       <c r="O45" t="n">
-        <v>0.006804</v>
+        <v>0.006153</v>
       </c>
       <c r="P45" t="n">
-        <v>0.022856</v>
+        <v>0.019589</v>
       </c>
       <c r="Q45" t="n">
         <v>9</v>
@@ -2799,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>0.013961</v>
+        <v>0.012951</v>
       </c>
     </row>
     <row r="46">
@@ -2809,58 +2809,58 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8905</v>
+        <v>0.891375</v>
       </c>
       <c r="D46" t="n">
-        <v>0.122079</v>
+        <v>0.117707</v>
       </c>
       <c r="E46" t="n">
-        <v>0.004316</v>
+        <v>0.003722</v>
       </c>
       <c r="F46" t="n">
-        <v>0.88204</v>
+        <v>0.884405</v>
       </c>
       <c r="G46" t="n">
-        <v>0.89896</v>
+        <v>0.898995</v>
       </c>
       <c r="H46" t="n">
-        <v>0.965417</v>
+        <v>0.967134</v>
       </c>
       <c r="I46" t="n">
-        <v>0.957334</v>
+        <v>0.961734</v>
       </c>
       <c r="J46" t="n">
-        <v>0.972467</v>
+        <v>0.974908</v>
       </c>
       <c r="K46" t="n">
-        <v>0.71875</v>
+        <v>0.719583</v>
       </c>
       <c r="L46" t="n">
-        <v>0.686606</v>
+        <v>0.692396</v>
       </c>
       <c r="M46" t="n">
-        <v>0.748803</v>
+        <v>0.747912</v>
       </c>
       <c r="N46" t="n">
-        <v>0.00625</v>
+        <v>0.007083</v>
       </c>
       <c r="O46" t="n">
-        <v>0.002672</v>
+        <v>0.003395</v>
       </c>
       <c r="P46" t="n">
-        <v>0.014547</v>
+        <v>0.014378</v>
       </c>
       <c r="Q46" t="n">
         <v>9</v>
       </c>
       <c r="R46" t="n">
-        <v>0.723951</v>
+        <v>0.722419</v>
       </c>
       <c r="S46" t="n">
-        <v>0.007926000000000001</v>
+        <v>0.007936</v>
       </c>
     </row>
     <row r="47">
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -2891,7 +2891,7 @@
         <v>0.99875</v>
       </c>
       <c r="I47" t="n">
-        <v>0.996875</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -2900,19 +2900,19 @@
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.995221</v>
+        <v>0.996173</v>
       </c>
       <c r="M47" t="n">
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0.0125</v>
+        <v>0.014167</v>
       </c>
       <c r="O47" t="n">
-        <v>0.006804</v>
+        <v>0.007613</v>
       </c>
       <c r="P47" t="n">
-        <v>0.022856</v>
+        <v>0.022114</v>
       </c>
       <c r="Q47" t="n">
         <v>9</v>
@@ -2921,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>0.013875</v>
+        <v>0.014989</v>
       </c>
     </row>
     <row r="48">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -2949,10 +2949,10 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0.999375</v>
+        <v>0.999583</v>
       </c>
       <c r="I48" t="n">
-        <v>0.998125</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -2961,19 +2961,19 @@
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0.995221</v>
+        <v>0.996173</v>
       </c>
       <c r="M48" t="n">
         <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>0.00625</v>
+        <v>0.006667</v>
       </c>
       <c r="O48" t="n">
-        <v>0.002672</v>
+        <v>0.002753</v>
       </c>
       <c r="P48" t="n">
-        <v>0.014547</v>
+        <v>0.013028</v>
       </c>
       <c r="Q48" t="n">
         <v>9</v>
@@ -2982,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>0.007754</v>
+        <v>0.007489</v>
       </c>
     </row>
     <row r="49">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -3022,19 +3022,19 @@
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.995221</v>
+        <v>0.996173</v>
       </c>
       <c r="M49" t="n">
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0075</v>
+        <v>0.008333</v>
       </c>
       <c r="O49" t="n">
-        <v>0.003442</v>
+        <v>0.004059</v>
       </c>
       <c r="P49" t="n">
-        <v>0.016265</v>
+        <v>0.015706</v>
       </c>
       <c r="Q49" t="n">
         <v>9</v>
@@ -3043,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.008789</v>
+        <v>0.00902</v>
       </c>
     </row>
     <row r="50">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -3083,19 +3083,19 @@
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.995221</v>
+        <v>0.996173</v>
       </c>
       <c r="M50" t="n">
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>0.005</v>
+        <v>0.0075</v>
       </c>
       <c r="O50" t="n">
-        <v>0.001946</v>
+        <v>0.003395</v>
       </c>
       <c r="P50" t="n">
-        <v>0.012785</v>
+        <v>0.014378</v>
       </c>
       <c r="Q50" t="n">
         <v>9</v>
@@ -3104,7 +3104,7 @@
         <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.006418</v>
+        <v>0.008345</v>
       </c>
     </row>
     <row r="51">
@@ -3114,7 +3114,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -3132,10 +3132,10 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0.999583</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -3144,19 +3144,19 @@
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.995221</v>
+        <v>0.996173</v>
       </c>
       <c r="M51" t="n">
         <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>0.0075</v>
+        <v>0.008333</v>
       </c>
       <c r="O51" t="n">
-        <v>0.003442</v>
+        <v>0.004059</v>
       </c>
       <c r="P51" t="n">
-        <v>0.016265</v>
+        <v>0.015706</v>
       </c>
       <c r="Q51" t="n">
         <v>9</v>
@@ -3165,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.009176</v>
+        <v>0.009223</v>
       </c>
     </row>
     <row r="52">
@@ -3175,58 +3175,58 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C52" t="n">
         <v>0.99775</v>
       </c>
       <c r="D52" t="n">
-        <v>0.028212</v>
+        <v>0.025247</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0009970000000000001</v>
+        <v>0.000798</v>
       </c>
       <c r="F52" t="n">
-        <v>0.995795</v>
+        <v>0.996635</v>
       </c>
       <c r="G52" t="n">
-        <v>0.999705</v>
+        <v>0.999765</v>
       </c>
       <c r="H52" t="n">
-        <v>0.998131</v>
+        <v>0.997715</v>
       </c>
       <c r="I52" t="n">
-        <v>0.995988</v>
+        <v>0.996163</v>
       </c>
       <c r="J52" t="n">
-        <v>0.999708</v>
+        <v>0.9995230000000001</v>
       </c>
       <c r="K52" t="n">
         <v>0.99375</v>
       </c>
       <c r="L52" t="n">
-        <v>0.985453</v>
+        <v>0.988349</v>
       </c>
       <c r="M52" t="n">
-        <v>0.997328</v>
+        <v>0.997862</v>
       </c>
       <c r="N52" t="n">
-        <v>0.0125</v>
+        <v>0.012083</v>
       </c>
       <c r="O52" t="n">
-        <v>0.006804</v>
+        <v>0.006878</v>
       </c>
       <c r="P52" t="n">
-        <v>0.022856</v>
+        <v>0.020857</v>
       </c>
       <c r="Q52" t="n">
         <v>9</v>
       </c>
       <c r="R52" t="n">
-        <v>0.993793</v>
+        <v>0.993773</v>
       </c>
       <c r="S52" t="n">
-        <v>0.013746</v>
+        <v>0.012709</v>
       </c>
     </row>
     <row r="53">
@@ -3236,58 +3236,772 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C53" t="n">
-        <v>0.781375</v>
+        <v>0.7847499999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>0.128106</v>
+        <v>0.126117</v>
       </c>
       <c r="E53" t="n">
-        <v>0.004529</v>
+        <v>0.003988</v>
       </c>
       <c r="F53" t="n">
-        <v>0.772498</v>
+        <v>0.7742830000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>0.790252</v>
+        <v>0.789917</v>
       </c>
       <c r="H53" t="n">
-        <v>0.903994</v>
+        <v>0.906405</v>
       </c>
       <c r="I53" t="n">
-        <v>0.888645</v>
+        <v>0.890829</v>
       </c>
       <c r="J53" t="n">
-        <v>0.917807</v>
+        <v>0.916146</v>
       </c>
       <c r="K53" t="n">
-        <v>0.31125</v>
+        <v>0.32</v>
       </c>
       <c r="L53" t="n">
-        <v>0.280132</v>
+        <v>0.285992</v>
       </c>
       <c r="M53" t="n">
-        <v>0.344172</v>
+        <v>0.343431</v>
       </c>
       <c r="N53" t="n">
-        <v>0.01</v>
+        <v>0.0125</v>
       </c>
       <c r="O53" t="n">
-        <v>0.005076</v>
+        <v>0.007613</v>
       </c>
       <c r="P53" t="n">
-        <v>0.019608</v>
+        <v>0.022114</v>
       </c>
       <c r="Q53" t="n">
         <v>9</v>
       </c>
       <c r="R53" t="n">
-        <v>0.321264</v>
+        <v>0.325354</v>
       </c>
       <c r="S53" t="n">
-        <v>0.011891</v>
+        <v>0.013473</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>distortion</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>bit_acc</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>acc_std</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>acc_sem</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>acc_ci_lo</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>acc_ci_hi</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>auc</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>auc_ci_lo</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>auc_ci_hi</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>tpr</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>tpr_ci_lo</t>
+        </is>
+      </c>
+      <c r="M56" s="1" t="inlineStr">
+        <is>
+          <t>tpr_ci_hi</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>fpr</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>fpr_ci_lo</t>
+        </is>
+      </c>
+      <c r="P56" s="1" t="inlineStr">
+        <is>
+          <t>fpr_ci_hi</t>
+        </is>
+      </c>
+      <c r="Q56" s="1" t="inlineStr">
+        <is>
+          <t>threshold_bits</t>
+        </is>
+      </c>
+      <c r="R56" s="1" t="inlineStr">
+        <is>
+          <t>tpr_at_exactly_1pct_fpr</t>
+        </is>
+      </c>
+      <c r="S56" s="1" t="inlineStr">
+        <is>
+          <t>fpr_randomized</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>No Distortion</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>100</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.9630069999999999</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.036993</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>26</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Resample (8k)</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>100</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.184484</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.018448</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.872842</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.9451580000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.9199000000000001</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.956808</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.7557970000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.899047</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.036993</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>26</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gaussian Noise</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>100</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.49425</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.045206</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.004521</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.48539</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.5031099999999999</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.4765</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.413445</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.543705</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.005502</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.070012</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.015663</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.098371</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>26</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Median Filter</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>100</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.98825</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.073723</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.007372</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.973801</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.002699</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.96995</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.945514</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.998233</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.001767</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.054486</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>26</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Low-pass 4k</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>100</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.95025</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.140728</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.014073</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.922668</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.977832</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.9571</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.9278999999999999</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.983751</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.837738</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.951927</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.005502</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.070012</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>26</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High-pass 500</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>100</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.098901</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.009889999999999999</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.957616</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.996384</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.9796</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.956341</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.995251</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.901629</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.984337</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.005502</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.070012</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>26</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Reencode</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>100</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.9630069999999999</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.036993</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>26</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Compression</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>100</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.9630069999999999</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.036993</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>26</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Noise Suppression</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>100</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.91575</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.170918</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.017092</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.882251</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.949249</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.9291</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.885396</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.962804</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.778628</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.914737</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.036993</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>26</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Phone Call</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>100</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.49875</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.034702</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.00347</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.491949</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.505551</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.5054999999999999</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.455095</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.555554</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.001767</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.054486</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.001767</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.054486</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>26</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -3301,7 +4015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4136,7 +4850,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -4166,19 +4880,19 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.006667</v>
+        <v>0.008</v>
       </c>
       <c r="O18" t="n">
-        <v>0.001178</v>
+        <v>0.002197</v>
       </c>
       <c r="P18" t="n">
-        <v>0.036793</v>
+        <v>0.028695</v>
       </c>
       <c r="Q18" t="n">
         <v>13</v>
@@ -4187,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.006834</v>
+        <v>0.008479</v>
       </c>
     </row>
     <row r="19">
@@ -4197,7 +4911,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -4227,19 +4941,19 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.013333</v>
+        <v>0.012</v>
       </c>
       <c r="O19" t="n">
-        <v>0.003664</v>
+        <v>0.004089</v>
       </c>
       <c r="P19" t="n">
-        <v>0.047307</v>
+        <v>0.034681</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -4248,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.013501</v>
+        <v>0.012598</v>
       </c>
     </row>
     <row r="20">
@@ -4258,58 +4972,58 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8125</v>
+        <v>0.81625</v>
       </c>
       <c r="D20" t="n">
-        <v>0.123311</v>
+        <v>0.124125</v>
       </c>
       <c r="E20" t="n">
-        <v>0.010068</v>
+        <v>0.007849999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.792767</v>
+        <v>0.800864</v>
       </c>
       <c r="G20" t="n">
-        <v>0.832233</v>
+        <v>0.831636</v>
       </c>
       <c r="H20" t="n">
-        <v>0.945444</v>
+        <v>0.95764</v>
       </c>
       <c r="I20" t="n">
-        <v>0.918303</v>
+        <v>0.941006</v>
       </c>
       <c r="J20" t="n">
-        <v>0.968297</v>
+        <v>0.9720569999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.66</v>
+        <v>0.652</v>
       </c>
       <c r="L20" t="n">
-        <v>0.581043</v>
+        <v>0.5910570000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.730967</v>
+        <v>0.7083429999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>0.026667</v>
+        <v>0.016</v>
       </c>
       <c r="O20" t="n">
-        <v>0.010418</v>
+        <v>0.006239</v>
       </c>
       <c r="P20" t="n">
-        <v>0.066554</v>
+        <v>0.04041</v>
       </c>
       <c r="Q20" t="n">
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>0.663019</v>
+        <v>0.655709</v>
       </c>
       <c r="S20" t="n">
-        <v>0.028176</v>
+        <v>0.017316</v>
       </c>
     </row>
     <row r="21">
@@ -4319,7 +5033,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -4349,19 +5063,19 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.006667</v>
+        <v>0.008</v>
       </c>
       <c r="O21" t="n">
-        <v>0.001178</v>
+        <v>0.002197</v>
       </c>
       <c r="P21" t="n">
-        <v>0.036793</v>
+        <v>0.028695</v>
       </c>
       <c r="Q21" t="n">
         <v>13</v>
@@ -4370,7 +5084,7 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.00717</v>
+        <v>0.008838</v>
       </c>
     </row>
     <row r="22">
@@ -4380,7 +5094,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -4410,19 +5124,19 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.006667</v>
+        <v>0.008</v>
       </c>
       <c r="O22" t="n">
-        <v>0.001178</v>
+        <v>0.002197</v>
       </c>
       <c r="P22" t="n">
-        <v>0.036793</v>
+        <v>0.028695</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
@@ -4431,7 +5145,7 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.007338</v>
+        <v>0.008838</v>
       </c>
     </row>
     <row r="23">
@@ -4441,7 +5155,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -4471,19 +5185,19 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.013333</v>
+        <v>0.008</v>
       </c>
       <c r="O23" t="n">
-        <v>0.003664</v>
+        <v>0.002197</v>
       </c>
       <c r="P23" t="n">
-        <v>0.047307</v>
+        <v>0.028695</v>
       </c>
       <c r="Q23" t="n">
         <v>13</v>
@@ -4492,7 +5206,7 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.013501</v>
+        <v>0.00812</v>
       </c>
     </row>
     <row r="24">
@@ -4502,7 +5216,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -4532,19 +5246,19 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.006667</v>
+        <v>0.008</v>
       </c>
       <c r="O24" t="n">
-        <v>0.001178</v>
+        <v>0.002197</v>
       </c>
       <c r="P24" t="n">
-        <v>0.036793</v>
+        <v>0.028695</v>
       </c>
       <c r="Q24" t="n">
         <v>13</v>
@@ -4553,7 +5267,7 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.006834</v>
+        <v>0.008479</v>
       </c>
     </row>
     <row r="25">
@@ -4563,7 +5277,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -4593,19 +5307,19 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.013333</v>
+        <v>0.008</v>
       </c>
       <c r="O25" t="n">
-        <v>0.003664</v>
+        <v>0.002197</v>
       </c>
       <c r="P25" t="n">
-        <v>0.047307</v>
+        <v>0.028695</v>
       </c>
       <c r="Q25" t="n">
         <v>13</v>
@@ -4614,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.014004</v>
+        <v>0.008957</v>
       </c>
     </row>
     <row r="26">
@@ -4624,58 +5338,58 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C26" t="n">
-        <v>0.99625</v>
+        <v>0.99775</v>
       </c>
       <c r="D26" t="n">
-        <v>0.036371</v>
+        <v>0.028196</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00297</v>
+        <v>0.001783</v>
       </c>
       <c r="F26" t="n">
-        <v>0.990429</v>
+        <v>0.994255</v>
       </c>
       <c r="G26" t="n">
-        <v>1.002071</v>
+        <v>1.001245</v>
       </c>
       <c r="H26" t="n">
-        <v>0.997844</v>
+        <v>0.998712</v>
       </c>
       <c r="I26" t="n">
-        <v>0.992667</v>
+        <v>0.995752</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0.993333</v>
+        <v>0.996</v>
       </c>
       <c r="L26" t="n">
-        <v>0.963207</v>
+        <v>0.977694</v>
       </c>
       <c r="M26" t="n">
-        <v>0.998822</v>
+        <v>0.999294</v>
       </c>
       <c r="N26" t="n">
-        <v>0.013333</v>
+        <v>0.016</v>
       </c>
       <c r="O26" t="n">
-        <v>0.003664</v>
+        <v>0.006239</v>
       </c>
       <c r="P26" t="n">
-        <v>0.047307</v>
+        <v>0.04041</v>
       </c>
       <c r="Q26" t="n">
         <v>13</v>
       </c>
       <c r="R26" t="n">
-        <v>0.993333</v>
+        <v>0.996</v>
       </c>
       <c r="S26" t="n">
-        <v>0.014004</v>
+        <v>0.016838</v>
       </c>
     </row>
     <row r="27">
@@ -4685,58 +5399,58 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5325</v>
+        <v>0.5277500000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.118479</v>
+        <v>0.12219</v>
       </c>
       <c r="E27" t="n">
-        <v>0.009674</v>
+        <v>0.007728</v>
       </c>
       <c r="F27" t="n">
-        <v>0.51354</v>
+        <v>0.5126039999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.55146</v>
+        <v>0.542896</v>
       </c>
       <c r="H27" t="n">
-        <v>0.579956</v>
+        <v>0.558424</v>
       </c>
       <c r="I27" t="n">
-        <v>0.513798</v>
+        <v>0.506441</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6444260000000001</v>
+        <v>0.6120100000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.006667</v>
+        <v>0.012</v>
       </c>
       <c r="L27" t="n">
-        <v>0.001178</v>
+        <v>0.004089</v>
       </c>
       <c r="M27" t="n">
-        <v>0.036793</v>
+        <v>0.034681</v>
       </c>
       <c r="N27" t="n">
-        <v>0.013333</v>
+        <v>0.012</v>
       </c>
       <c r="O27" t="n">
-        <v>0.003664</v>
+        <v>0.004089</v>
       </c>
       <c r="P27" t="n">
-        <v>0.047307</v>
+        <v>0.034681</v>
       </c>
       <c r="Q27" t="n">
         <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>0.008512</v>
+        <v>0.013915</v>
       </c>
       <c r="S27" t="n">
-        <v>0.014172</v>
+        <v>0.013316</v>
       </c>
     </row>
     <row r="29">
@@ -5615,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.011891</v>
+        <v>0.010995</v>
       </c>
     </row>
     <row r="45">
@@ -5676,7 +6390,7 @@
         <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>0.019649</v>
+        <v>0.018631</v>
       </c>
     </row>
     <row r="46">
@@ -5734,10 +6448,10 @@
         <v>9</v>
       </c>
       <c r="R46" t="n">
-        <v>0.717658</v>
+        <v>0.715215</v>
       </c>
       <c r="S46" t="n">
-        <v>0.009305000000000001</v>
+        <v>0.008449999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -5798,7 +6512,7 @@
         <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>0.021633</v>
+        <v>0.02086</v>
       </c>
     </row>
     <row r="48">
@@ -5859,7 +6573,7 @@
         <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>0.011805</v>
+        <v>0.01095</v>
       </c>
     </row>
     <row r="49">
@@ -5920,7 +6634,7 @@
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.011633</v>
+        <v>0.01086</v>
       </c>
     </row>
     <row r="50">
@@ -5981,7 +6695,7 @@
         <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.011891</v>
+        <v>0.010995</v>
       </c>
     </row>
     <row r="51">
@@ -6042,7 +6756,7 @@
         <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.012063</v>
+        <v>0.011086</v>
       </c>
     </row>
     <row r="52">
@@ -6100,10 +6814,10 @@
         <v>9</v>
       </c>
       <c r="R52" t="n">
-        <v>0.987586</v>
+        <v>0.987545</v>
       </c>
       <c r="S52" t="n">
-        <v>0.013789</v>
+        <v>0.013179</v>
       </c>
     </row>
     <row r="53">
@@ -6161,10 +6875,724 @@
         <v>9</v>
       </c>
       <c r="R53" t="n">
-        <v>0.360315</v>
+        <v>0.35543</v>
       </c>
       <c r="S53" t="n">
-        <v>0.011805</v>
+        <v>0.01095</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>distortion</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>bit_acc</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>acc_std</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>acc_sem</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>acc_ci_lo</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>acc_ci_hi</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>auc</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>auc_ci_lo</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>auc_ci_hi</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>tpr</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>tpr_ci_lo</t>
+        </is>
+      </c>
+      <c r="M56" s="1" t="inlineStr">
+        <is>
+          <t>tpr_ci_hi</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>fpr</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>fpr_ci_lo</t>
+        </is>
+      </c>
+      <c r="P56" s="1" t="inlineStr">
+        <is>
+          <t>fpr_ci_hi</t>
+        </is>
+      </c>
+      <c r="Q56" s="1" t="inlineStr">
+        <is>
+          <t>threshold_bits</t>
+        </is>
+      </c>
+      <c r="R56" s="1" t="inlineStr">
+        <is>
+          <t>tpr_at_exactly_1pct_fpr</t>
+        </is>
+      </c>
+      <c r="S56" s="1" t="inlineStr">
+        <is>
+          <t>fpr_randomized</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>No Distortion</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>50</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>26</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Resample (8k)</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>50</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.9065</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.181744</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.025702</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.856124</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.9568759999999999</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.9184</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.9676</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.714858</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.9166260000000001</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>26</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gaussian Noise</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>50</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.046991</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.006646</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.480975</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.5070249999999999</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.4994</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.402785</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.6018250000000001</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.011039</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.134601</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>26</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Median Filter</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>50</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.9915</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.007057</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.977669</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.005331</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>26</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Low-pass 4k</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>50</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.119439</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.016891</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.9283940000000001</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.994606</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.9718</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.9342</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.837829</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.979385</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>26</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High-pass 500</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>50</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.09980700000000001</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.014115</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.947835</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.003165</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.865399</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.988961</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.011039</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.134601</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>26</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Reencode</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>50</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>26</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Compression</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>50</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>26</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Noise Suppression</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>50</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.186589</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.026388</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.8392810000000001</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.942719</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.8539949999999999</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.965605</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.692039</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.902298</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>26</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Phone Call</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>50</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.033308</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.00471</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.490268</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.508732</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.4908</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.422995</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.564405</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>26</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -6178,7 +7606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7013,7 +8441,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -7043,19 +8471,19 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.005</v>
+        <v>0.003333</v>
       </c>
       <c r="O18" t="n">
-        <v>0.000883</v>
+        <v>0.000589</v>
       </c>
       <c r="P18" t="n">
-        <v>0.027774</v>
+        <v>0.018637</v>
       </c>
       <c r="Q18" t="n">
         <v>13</v>
@@ -7064,7 +8492,7 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005629</v>
+        <v>0.004031</v>
       </c>
     </row>
     <row r="19">
@@ -7074,7 +8502,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -7104,19 +8532,19 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="O19" t="n">
-        <v>0.005114</v>
+        <v>0.003407</v>
       </c>
       <c r="P19" t="n">
-        <v>0.043166</v>
+        <v>0.028983</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -7125,7 +8553,7 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.015252</v>
+        <v>0.010499</v>
       </c>
     </row>
     <row r="20">
@@ -7135,58 +8563,58 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C20" t="n">
-        <v>0.815625</v>
+        <v>0.814792</v>
       </c>
       <c r="D20" t="n">
-        <v>0.102717</v>
+        <v>0.108229</v>
       </c>
       <c r="E20" t="n">
-        <v>0.007263</v>
+        <v>0.006249</v>
       </c>
       <c r="F20" t="n">
-        <v>0.801389</v>
+        <v>0.802545</v>
       </c>
       <c r="G20" t="n">
-        <v>0.829861</v>
+        <v>0.827039</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9779870000000001</v>
+        <v>0.974456</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9665820000000001</v>
+        <v>0.964239</v>
       </c>
       <c r="J20" t="n">
-        <v>0.987726</v>
+        <v>0.983145</v>
       </c>
       <c r="K20" t="n">
-        <v>0.655</v>
+        <v>0.656667</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5867560000000001</v>
+        <v>0.60126</v>
       </c>
       <c r="M20" t="n">
-        <v>0.717402</v>
+        <v>0.708112</v>
       </c>
       <c r="N20" t="n">
-        <v>0.005</v>
+        <v>0.006667</v>
       </c>
       <c r="O20" t="n">
-        <v>0.000883</v>
+        <v>0.00183</v>
       </c>
       <c r="P20" t="n">
-        <v>0.027774</v>
+        <v>0.023978</v>
       </c>
       <c r="Q20" t="n">
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>0.659403</v>
+        <v>0.661752</v>
       </c>
       <c r="S20" t="n">
-        <v>0.005503</v>
+        <v>0.007165</v>
       </c>
     </row>
     <row r="21">
@@ -7196,7 +8624,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -7226,19 +8654,19 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.01</v>
+        <v>0.006667</v>
       </c>
       <c r="O21" t="n">
-        <v>0.002747</v>
+        <v>0.00183</v>
       </c>
       <c r="P21" t="n">
-        <v>0.035722</v>
+        <v>0.023978</v>
       </c>
       <c r="Q21" t="n">
         <v>13</v>
@@ -7247,7 +8675,7 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.010755</v>
+        <v>0.007365</v>
       </c>
     </row>
     <row r="22">
@@ -7257,7 +8685,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -7287,19 +8715,19 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="O22" t="n">
-        <v>0.005114</v>
+        <v>0.003407</v>
       </c>
       <c r="P22" t="n">
-        <v>0.043166</v>
+        <v>0.028983</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
@@ -7308,7 +8736,7 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.015503</v>
+        <v>0.010798</v>
       </c>
     </row>
     <row r="23">
@@ -7318,7 +8746,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -7348,19 +8776,19 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.003333</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>0.000589</v>
       </c>
       <c r="P23" t="n">
-        <v>0.018845</v>
+        <v>0.018637</v>
       </c>
       <c r="Q23" t="n">
         <v>13</v>
@@ -7369,7 +8797,7 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.000629</v>
+        <v>0.004231</v>
       </c>
     </row>
     <row r="24">
@@ -7379,7 +8807,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -7409,19 +8837,19 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.005</v>
+        <v>0.003333</v>
       </c>
       <c r="O24" t="n">
-        <v>0.000883</v>
+        <v>0.000589</v>
       </c>
       <c r="P24" t="n">
-        <v>0.027774</v>
+        <v>0.018637</v>
       </c>
       <c r="Q24" t="n">
         <v>13</v>
@@ -7430,7 +8858,7 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.005629</v>
+        <v>0.004031</v>
       </c>
     </row>
     <row r="25">
@@ -7440,7 +8868,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -7470,19 +8898,19 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.01</v>
+        <v>0.006667</v>
       </c>
       <c r="O25" t="n">
-        <v>0.002747</v>
+        <v>0.00183</v>
       </c>
       <c r="P25" t="n">
-        <v>0.035722</v>
+        <v>0.023978</v>
       </c>
       <c r="Q25" t="n">
         <v>13</v>
@@ -7491,7 +8919,7 @@
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.010755</v>
+        <v>0.007365</v>
       </c>
     </row>
     <row r="26">
@@ -7501,7 +8929,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -7531,19 +8959,19 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.005</v>
+        <v>0.003333</v>
       </c>
       <c r="O26" t="n">
-        <v>0.000883</v>
+        <v>0.000589</v>
       </c>
       <c r="P26" t="n">
-        <v>0.027774</v>
+        <v>0.018637</v>
       </c>
       <c r="Q26" t="n">
         <v>13</v>
@@ -7552,7 +8980,7 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.006635</v>
+        <v>0.004829</v>
       </c>
     </row>
     <row r="27">
@@ -7562,58 +8990,58 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C27" t="n">
-        <v>0.537188</v>
+        <v>0.530625</v>
       </c>
       <c r="D27" t="n">
-        <v>0.129033</v>
+        <v>0.128248</v>
       </c>
       <c r="E27" t="n">
-        <v>0.009124</v>
+        <v>0.007404</v>
       </c>
       <c r="F27" t="n">
-        <v>0.519305</v>
+        <v>0.516113</v>
       </c>
       <c r="G27" t="n">
-        <v>0.55507</v>
+        <v>0.545137</v>
       </c>
       <c r="H27" t="n">
-        <v>0.56525</v>
+        <v>0.564411</v>
       </c>
       <c r="I27" t="n">
-        <v>0.51131</v>
+        <v>0.517215</v>
       </c>
       <c r="J27" t="n">
-        <v>0.620413</v>
+        <v>0.610098</v>
       </c>
       <c r="K27" t="n">
         <v>0.03</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01382</v>
+        <v>0.015862</v>
       </c>
       <c r="M27" t="n">
-        <v>0.06389400000000001</v>
+        <v>0.056023</v>
       </c>
       <c r="N27" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="O27" t="n">
-        <v>0.000883</v>
+        <v>0.003407</v>
       </c>
       <c r="P27" t="n">
-        <v>0.027774</v>
+        <v>0.028983</v>
       </c>
       <c r="Q27" t="n">
         <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>0.030881</v>
+        <v>0.030997</v>
       </c>
       <c r="S27" t="n">
-        <v>0.006006</v>
+        <v>0.010897</v>
       </c>
     </row>
     <row r="29">
@@ -8441,7 +9869,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -8471,19 +9899,19 @@
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="M44" t="n">
         <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>0.001702</v>
       </c>
       <c r="P44" t="n">
-        <v>0.009512</v>
+        <v>0.014596</v>
       </c>
       <c r="Q44" t="n">
         <v>9</v>
@@ -8492,7 +9920,7 @@
         <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.001032</v>
+        <v>0.005724</v>
       </c>
     </row>
     <row r="45">
@@ -8502,7 +9930,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -8532,19 +9960,19 @@
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>0.0075</v>
+        <v>0.006667</v>
       </c>
       <c r="O45" t="n">
-        <v>0.002554</v>
+        <v>0.002596</v>
       </c>
       <c r="P45" t="n">
-        <v>0.021816</v>
+        <v>0.017015</v>
       </c>
       <c r="Q45" t="n">
         <v>9</v>
@@ -8553,7 +9981,7 @@
         <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>0.008274</v>
+        <v>0.00727</v>
       </c>
     </row>
     <row r="46">
@@ -8563,58 +9991,58 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C46" t="n">
-        <v>0.89125</v>
+        <v>0.893</v>
       </c>
       <c r="D46" t="n">
-        <v>0.116328</v>
+        <v>0.110626</v>
       </c>
       <c r="E46" t="n">
-        <v>0.005816</v>
+        <v>0.004516</v>
       </c>
       <c r="F46" t="n">
-        <v>0.87985</v>
+        <v>0.884148</v>
       </c>
       <c r="G46" t="n">
-        <v>0.90265</v>
+        <v>0.901852</v>
       </c>
       <c r="H46" t="n">
-        <v>0.969834</v>
+        <v>0.973268</v>
       </c>
       <c r="I46" t="n">
-        <v>0.959646</v>
+        <v>0.965524</v>
       </c>
       <c r="J46" t="n">
-        <v>0.979166</v>
+        <v>0.980824</v>
       </c>
       <c r="K46" t="n">
-        <v>0.725</v>
+        <v>0.726667</v>
       </c>
       <c r="L46" t="n">
-        <v>0.679258</v>
+        <v>0.689649</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7664609999999999</v>
+        <v>0.7608009999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>0.005</v>
+        <v>0.006667</v>
       </c>
       <c r="O46" t="n">
-        <v>0.001372</v>
+        <v>0.002596</v>
       </c>
       <c r="P46" t="n">
-        <v>0.018045</v>
+        <v>0.017015</v>
       </c>
       <c r="Q46" t="n">
         <v>9</v>
       </c>
       <c r="R46" t="n">
-        <v>0.730244</v>
+        <v>0.729623</v>
       </c>
       <c r="S46" t="n">
-        <v>0.006547</v>
+        <v>0.007421</v>
       </c>
     </row>
     <row r="47">
@@ -8624,7 +10052,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -8654,19 +10082,19 @@
         <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="M47" t="n">
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0.005</v>
+        <v>0.008333</v>
       </c>
       <c r="O47" t="n">
-        <v>0.001372</v>
+        <v>0.003565</v>
       </c>
       <c r="P47" t="n">
-        <v>0.018045</v>
+        <v>0.019358</v>
       </c>
       <c r="Q47" t="n">
         <v>9</v>
@@ -8675,7 +10103,7 @@
         <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>0.006117</v>
+        <v>0.009117999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -8685,7 +10113,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -8703,10 +10131,10 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>0.99875</v>
+        <v>0.999167</v>
       </c>
       <c r="I48" t="n">
-        <v>0.99625</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -8715,19 +10143,19 @@
         <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="M48" t="n">
         <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>0.0025</v>
+        <v>0.003333</v>
       </c>
       <c r="O48" t="n">
-        <v>0.000441</v>
+        <v>0.000915</v>
       </c>
       <c r="P48" t="n">
-        <v>0.014023</v>
+        <v>0.012071</v>
       </c>
       <c r="Q48" t="n">
         <v>9</v>
@@ -8736,7 +10164,7 @@
         <v>1</v>
       </c>
       <c r="S48" t="n">
-        <v>0.003703</v>
+        <v>0.004027</v>
       </c>
     </row>
     <row r="49">
@@ -8746,7 +10174,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -8776,19 +10204,19 @@
         <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="M49" t="n">
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>0.005</v>
+        <v>0.006667</v>
       </c>
       <c r="O49" t="n">
-        <v>0.001372</v>
+        <v>0.002596</v>
       </c>
       <c r="P49" t="n">
-        <v>0.018045</v>
+        <v>0.017015</v>
       </c>
       <c r="Q49" t="n">
         <v>9</v>
@@ -8797,7 +10225,7 @@
         <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.005946</v>
+        <v>0.007179</v>
       </c>
     </row>
     <row r="50">
@@ -8807,7 +10235,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -8837,19 +10265,19 @@
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="M50" t="n">
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>0.001702</v>
       </c>
       <c r="P50" t="n">
-        <v>0.009512</v>
+        <v>0.014596</v>
       </c>
       <c r="Q50" t="n">
         <v>9</v>
@@ -8858,7 +10286,7 @@
         <v>1</v>
       </c>
       <c r="S50" t="n">
-        <v>0.000946</v>
+        <v>0.005694</v>
       </c>
     </row>
     <row r="51">
@@ -8868,7 +10296,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -8886,10 +10314,10 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0.999167</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -8898,19 +10326,19 @@
         <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="M51" t="n">
         <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>0.005</v>
+        <v>0.006667</v>
       </c>
       <c r="O51" t="n">
-        <v>0.001372</v>
+        <v>0.002596</v>
       </c>
       <c r="P51" t="n">
-        <v>0.018045</v>
+        <v>0.017015</v>
       </c>
       <c r="Q51" t="n">
         <v>9</v>
@@ -8919,7 +10347,7 @@
         <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.006289</v>
+        <v>0.00736</v>
       </c>
     </row>
     <row r="52">
@@ -8929,7 +10357,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -8947,10 +10375,10 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0.999167</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -8959,19 +10387,19 @@
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="M52" t="n">
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>0.0125</v>
+        <v>0.011667</v>
       </c>
       <c r="O52" t="n">
-        <v>0.005351</v>
+        <v>0.005663</v>
       </c>
       <c r="P52" t="n">
-        <v>0.028924</v>
+        <v>0.023884</v>
       </c>
       <c r="Q52" t="n">
         <v>9</v>
@@ -8980,7 +10408,7 @@
         <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.013703</v>
+        <v>0.01224</v>
       </c>
     </row>
     <row r="53">
@@ -8990,58 +10418,772 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C53" t="n">
-        <v>0.76475</v>
+        <v>0.7715</v>
       </c>
       <c r="D53" t="n">
-        <v>0.129322</v>
+        <v>0.125953</v>
       </c>
       <c r="E53" t="n">
-        <v>0.006466</v>
+        <v>0.005142</v>
       </c>
       <c r="F53" t="n">
-        <v>0.752077</v>
+        <v>0.761422</v>
       </c>
       <c r="G53" t="n">
-        <v>0.777423</v>
+        <v>0.781578</v>
       </c>
       <c r="H53" t="n">
-        <v>0.892753</v>
+        <v>0.897576</v>
       </c>
       <c r="I53" t="n">
-        <v>0.871702</v>
+        <v>0.879615</v>
       </c>
       <c r="J53" t="n">
-        <v>0.912431</v>
+        <v>0.913436</v>
       </c>
       <c r="K53" t="n">
-        <v>0.2725</v>
+        <v>0.29</v>
       </c>
       <c r="L53" t="n">
-        <v>0.231185</v>
+        <v>0.255119</v>
       </c>
       <c r="M53" t="n">
-        <v>0.318143</v>
+        <v>0.327553</v>
       </c>
       <c r="N53" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="O53" t="n">
-        <v>0.003895</v>
+        <v>0.007911</v>
       </c>
       <c r="P53" t="n">
-        <v>0.025427</v>
+        <v>0.02826</v>
       </c>
       <c r="Q53" t="n">
         <v>9</v>
       </c>
       <c r="R53" t="n">
-        <v>0.282213</v>
+        <v>0.295279</v>
       </c>
       <c r="S53" t="n">
-        <v>0.011977</v>
+        <v>0.015995</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>distortion</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>bit_acc</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>acc_std</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>acc_sem</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>acc_ci_lo</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>acc_ci_hi</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>auc</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>auc_ci_lo</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>auc_ci_hi</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="inlineStr">
+        <is>
+          <t>tpr</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>tpr_ci_lo</t>
+        </is>
+      </c>
+      <c r="M56" s="1" t="inlineStr">
+        <is>
+          <t>tpr_ci_hi</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>fpr</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>fpr_ci_lo</t>
+        </is>
+      </c>
+      <c r="P56" s="1" t="inlineStr">
+        <is>
+          <t>fpr_ci_hi</t>
+        </is>
+      </c>
+      <c r="Q56" s="1" t="inlineStr">
+        <is>
+          <t>threshold_bits</t>
+        </is>
+      </c>
+      <c r="R56" s="1" t="inlineStr">
+        <is>
+          <t>tpr_at_exactly_1pct_fpr</t>
+        </is>
+      </c>
+      <c r="S56" s="1" t="inlineStr">
+        <is>
+          <t>fpr_randomized</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>No Distortion</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>50</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>26</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Resample (8k)</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>50</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.9115</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.188996</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.026728</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.859114</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.963886</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.9214</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.858985</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.97061</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.714858</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.9166260000000001</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>26</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Gaussian Noise</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>50</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.043825</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.006198</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.482352</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.506648</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.360995</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.548005</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.011039</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.134601</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>26</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Median Filter</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>50</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.092029</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.013015</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.959491</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.010509</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.895046</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.996461</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>26</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Low-pass 4k</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>50</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.159652</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.022578</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.894748</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.983252</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.9424</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.8943950000000001</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.985605</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.761952</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.943824</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>26</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>High-pass 500</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>50</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.9785</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.09897599999999999</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.013997</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.951066</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1.005934</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.9792</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.865399</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.988961</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>26</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Reencode</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>50</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>26</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Compression</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>50</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>26</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Noise Suppression</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>50</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.151514</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.021427</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.8985030000000001</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.982497</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.9452</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.88878</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.9882</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.786398</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.956524</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>26</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Phone Call</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>50</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.036365</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.005143</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.48792</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.50808</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.4482</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.592005</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>26</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9890,7 +12032,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -9920,19 +12062,19 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="O18" t="n">
-        <v>0.004089</v>
+        <v>0.006892</v>
       </c>
       <c r="P18" t="n">
-        <v>0.034681</v>
+        <v>0.032335</v>
       </c>
       <c r="Q18" t="n">
         <v>13</v>
@@ -9941,7 +12083,7 @@
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.012704</v>
+        <v>0.015524</v>
       </c>
     </row>
     <row r="19">
@@ -9951,7 +12093,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -9981,19 +12123,19 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="M19" t="n">
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.004</v>
+        <v>0.0125</v>
       </c>
       <c r="O19" t="n">
-        <v>0.000706</v>
+        <v>0.005351</v>
       </c>
       <c r="P19" t="n">
-        <v>0.022306</v>
+        <v>0.028924</v>
       </c>
       <c r="Q19" t="n">
         <v>13</v>
@@ -10002,7 +12144,7 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.004704</v>
+        <v>0.013098</v>
       </c>
     </row>
     <row r="20">
@@ -10012,58 +12154,58 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C20" t="n">
-        <v>0.757</v>
+        <v>0.757969</v>
       </c>
       <c r="D20" t="n">
-        <v>0.131654</v>
+        <v>0.130386</v>
       </c>
       <c r="E20" t="n">
-        <v>0.008326999999999999</v>
+        <v>0.006519</v>
       </c>
       <c r="F20" t="n">
-        <v>0.74068</v>
+        <v>0.745191</v>
       </c>
       <c r="G20" t="n">
-        <v>0.77332</v>
+        <v>0.770746</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9302240000000001</v>
+        <v>0.925872</v>
       </c>
       <c r="I20" t="n">
-        <v>0.91047</v>
+        <v>0.908322</v>
       </c>
       <c r="J20" t="n">
-        <v>0.948041</v>
+        <v>0.941805</v>
       </c>
       <c r="K20" t="n">
-        <v>0.456</v>
+        <v>0.46</v>
       </c>
       <c r="L20" t="n">
-        <v>0.395392</v>
+        <v>0.41177</v>
       </c>
       <c r="M20" t="n">
-        <v>0.51794</v>
+        <v>0.508991</v>
       </c>
       <c r="N20" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="O20" t="n">
-        <v>0.002197</v>
+        <v>0.003895</v>
       </c>
       <c r="P20" t="n">
-        <v>0.028695</v>
+        <v>0.025427</v>
       </c>
       <c r="Q20" t="n">
         <v>13</v>
       </c>
       <c r="R20" t="n">
-        <v>0.460226</v>
+        <v>0.465235</v>
       </c>
       <c r="S20" t="n">
-        <v>0.008503</v>
+        <v>0.010524</v>
       </c>
     </row>
     <row r="21">
@@ -10073,7 +12215,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -10103,19 +12245,19 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="O21" t="n">
-        <v>0.004089</v>
+        <v>0.003895</v>
       </c>
       <c r="P21" t="n">
-        <v>0.034681</v>
+        <v>0.025427</v>
       </c>
       <c r="Q21" t="n">
         <v>13</v>
@@ -10124,7 +12266,7 @@
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.012403</v>
+        <v>0.010598</v>
       </c>
     </row>
     <row r="22">
@@ -10134,7 +12276,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -10164,19 +12306,19 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.008</v>
+        <v>0.0125</v>
       </c>
       <c r="O22" t="n">
-        <v>0.002197</v>
+        <v>0.005351</v>
       </c>
       <c r="P22" t="n">
-        <v>0.028695</v>
+        <v>0.028924</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
@@ -10185,7 +12327,7 @@
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.009006</v>
+        <v>0.013248</v>
       </c>
     </row>
     <row r="23">
@@ -10195,7 +12337,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -10225,19 +12367,19 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="O23" t="n">
-        <v>0.002197</v>
+        <v>0.001372</v>
       </c>
       <c r="P23" t="n">
-        <v>0.028695</v>
+        <v>0.018045</v>
       </c>
       <c r="Q23" t="n">
         <v>13</v>
@@ -10246,7 +12388,7 @@
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.008704</v>
+        <v>0.005897</v>
       </c>
     </row>
     <row r="24">
@@ -10256,7 +12398,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -10286,19 +12428,19 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="O24" t="n">
-        <v>0.004089</v>
+        <v>0.006892</v>
       </c>
       <c r="P24" t="n">
-        <v>0.034681</v>
+        <v>0.032335</v>
       </c>
       <c r="Q24" t="n">
         <v>13</v>
@@ -10307,7 +12449,7 @@
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.012704</v>
+        <v>0.015524</v>
       </c>
     </row>
     <row r="25">
@@ -10317,7 +12459,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -10347,19 +12489,19 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="O25" t="n">
-        <v>0.006239</v>
+        <v>0.010168</v>
       </c>
       <c r="P25" t="n">
-        <v>0.04041</v>
+        <v>0.038963</v>
       </c>
       <c r="Q25" t="n">
         <v>13</v>
@@ -10368,7 +12510,7 @@
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.016906</v>
+        <v>0.020748</v>
       </c>
     </row>
     <row r="26">
@@ -10378,22 +12520,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.998906</v>
       </c>
       <c r="D26" t="n">
-        <v>0.009585</v>
+        <v>0.008206</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000606</v>
+        <v>0.00041</v>
       </c>
       <c r="F26" t="n">
-        <v>0.997312</v>
+        <v>0.998102</v>
       </c>
       <c r="G26" t="n">
-        <v>0.999688</v>
+        <v>0.99971</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -10408,19 +12550,19 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.012</v>
+        <v>0.0075</v>
       </c>
       <c r="O26" t="n">
-        <v>0.004089</v>
+        <v>0.002554</v>
       </c>
       <c r="P26" t="n">
-        <v>0.034681</v>
+        <v>0.021816</v>
       </c>
       <c r="Q26" t="n">
         <v>13</v>
@@ -10429,7 +12571,7 @@
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.012704</v>
+        <v>0.008397</v>
       </c>
     </row>
     <row r="27">
@@ -10439,40 +12581,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="C27" t="n">
-        <v>0.523</v>
+        <v>0.524844</v>
       </c>
       <c r="D27" t="n">
-        <v>0.126009</v>
+        <v>0.123653</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00797</v>
+        <v>0.006183</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5073800000000001</v>
+        <v>0.512726</v>
       </c>
       <c r="G27" t="n">
-        <v>0.53862</v>
+        <v>0.5369620000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.543632</v>
+        <v>0.565069</v>
       </c>
       <c r="I27" t="n">
-        <v>0.488739</v>
+        <v>0.525227</v>
       </c>
       <c r="J27" t="n">
-        <v>0.594282</v>
+        <v>0.60487</v>
       </c>
       <c r="K27" t="n">
         <v>0.02</v>
       </c>
       <c r="L27" t="n">
-        <v>0.008572</v>
+        <v>0.010168</v>
       </c>
       <c r="M27" t="n">
-        <v>0.045956</v>
+        <v>0.038963</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -10481,16 +12623,16 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.015133</v>
+        <v>0.009512</v>
       </c>
       <c r="Q27" t="n">
         <v>13</v>
       </c>
       <c r="R27" t="n">
-        <v>0.021208</v>
+        <v>0.021496</v>
       </c>
       <c r="S27" t="n">
-        <v>0.000503</v>
+        <v>0.000673</v>
       </c>
     </row>
     <row r="29">
@@ -11953,7 +14095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12039,10 +14181,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>6000</v>
+        <v>9500</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009332999999999999</v>
+        <v>0.009263</v>
       </c>
       <c r="F3" t="n">
         <v>0.01</v>
@@ -12051,7 +14193,7 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>0.025157</v>
+        <v>0.029915</v>
       </c>
     </row>
     <row r="4">
@@ -12095,10 +14237,10 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0092</v>
       </c>
       <c r="F5" t="n">
         <v>0.01</v>
@@ -12107,18 +14249,46 @@
         <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>0.034384</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Deterministic threshold: smallest integer bit count whose pooled FPR is &lt;= the target. Because the statistic is discrete the realised rate lands under the target, by a margin that depends on payload size.</t>
-        </is>
+        <v>0.0181</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>40</v>
+      </c>
+      <c r="C6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G6" t="n">
+        <v>26</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>Deterministic threshold: smallest integer bit count whose pooled FPR is &lt;= the target. Because the statistic is discrete the realised rate lands under the target, by a margin that depends on payload size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Randomized rule: reject when score &gt;= randomized_t, or when score == randomized_t - 1 with probability randomized_gamma. Hits the target FPR exactly for every payload size, so TPRs are comparable across methods.</t>
         </is>
@@ -12135,7 +14305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12912,6 +15082,184 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>3.6975</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LibriSpeech-dev</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2303</v>
+      </c>
+      <c r="D24" t="n">
+        <v>48.8968</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="F24" t="n">
+        <v>48.883</v>
+      </c>
+      <c r="G24" t="n">
+        <v>48.9106</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.5818</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.5795</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.5842</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LJSpeech</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D25" t="n">
+        <v>48.8637</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.1122</v>
+      </c>
+      <c r="F25" t="n">
+        <v>48.8595</v>
+      </c>
+      <c r="G25" t="n">
+        <v>48.868</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.5963</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.5957</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.597</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>clone_xspeaker</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1624</v>
+      </c>
+      <c r="D26" t="n">
+        <v>49.3216</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="F26" t="n">
+        <v>49.3079</v>
+      </c>
+      <c r="G26" t="n">
+        <v>49.3353</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.5882</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.5861</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.5903</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>resynth_hifigan</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D27" t="n">
+        <v>48.9393</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="F27" t="n">
+        <v>48.9229</v>
+      </c>
+      <c r="G27" t="n">
+        <v>48.9558</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.5936</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.5916</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.5956</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MEAN OF CORPORA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>49.0054</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>4.59</v>
       </c>
     </row>
   </sheetData>
@@ -12925,7 +15273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15892,7 +18240,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -15922,19 +18270,19 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>0.006667</v>
+        <v>0.008</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.001178</v>
+        <v>0.002197</v>
       </c>
       <c r="R42" t="n">
-        <v>0.036793</v>
+        <v>0.028695</v>
       </c>
       <c r="S42" t="n">
         <v>13</v>
@@ -15943,7 +18291,7 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0.006834</v>
+        <v>0.008479</v>
       </c>
     </row>
     <row r="43">
@@ -15963,7 +18311,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -15993,19 +18341,19 @@
         <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.013333</v>
+        <v>0.012</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.003664</v>
+        <v>0.004089</v>
       </c>
       <c r="R43" t="n">
-        <v>0.047307</v>
+        <v>0.034681</v>
       </c>
       <c r="S43" t="n">
         <v>13</v>
@@ -16014,7 +18362,7 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0.013501</v>
+        <v>0.012598</v>
       </c>
     </row>
     <row r="44">
@@ -16034,58 +18382,58 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8125</v>
+        <v>0.81625</v>
       </c>
       <c r="F44" t="n">
-        <v>0.123311</v>
+        <v>0.124125</v>
       </c>
       <c r="G44" t="n">
-        <v>0.010068</v>
+        <v>0.007849999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>0.792767</v>
+        <v>0.800864</v>
       </c>
       <c r="I44" t="n">
-        <v>0.832233</v>
+        <v>0.831636</v>
       </c>
       <c r="J44" t="n">
-        <v>0.945444</v>
+        <v>0.95764</v>
       </c>
       <c r="K44" t="n">
-        <v>0.918303</v>
+        <v>0.941006</v>
       </c>
       <c r="L44" t="n">
-        <v>0.968297</v>
+        <v>0.9720569999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>0.66</v>
+        <v>0.652</v>
       </c>
       <c r="N44" t="n">
-        <v>0.581043</v>
+        <v>0.5910570000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>0.730967</v>
+        <v>0.7083429999999999</v>
       </c>
       <c r="P44" t="n">
-        <v>0.026667</v>
+        <v>0.016</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.010418</v>
+        <v>0.006239</v>
       </c>
       <c r="R44" t="n">
-        <v>0.066554</v>
+        <v>0.04041</v>
       </c>
       <c r="S44" t="n">
         <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>0.663019</v>
+        <v>0.655709</v>
       </c>
       <c r="U44" t="n">
-        <v>0.028176</v>
+        <v>0.017316</v>
       </c>
     </row>
     <row r="45">
@@ -16105,7 +18453,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -16135,19 +18483,19 @@
         <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>0.006667</v>
+        <v>0.008</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.001178</v>
+        <v>0.002197</v>
       </c>
       <c r="R45" t="n">
-        <v>0.036793</v>
+        <v>0.028695</v>
       </c>
       <c r="S45" t="n">
         <v>13</v>
@@ -16156,7 +18504,7 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0.00717</v>
+        <v>0.008838</v>
       </c>
     </row>
     <row r="46">
@@ -16176,7 +18524,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -16206,19 +18554,19 @@
         <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>0.006667</v>
+        <v>0.008</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.001178</v>
+        <v>0.002197</v>
       </c>
       <c r="R46" t="n">
-        <v>0.036793</v>
+        <v>0.028695</v>
       </c>
       <c r="S46" t="n">
         <v>13</v>
@@ -16227,7 +18575,7 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0.007338</v>
+        <v>0.008838</v>
       </c>
     </row>
     <row r="47">
@@ -16247,7 +18595,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -16277,19 +18625,19 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0.013333</v>
+        <v>0.008</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.003664</v>
+        <v>0.002197</v>
       </c>
       <c r="R47" t="n">
-        <v>0.047307</v>
+        <v>0.028695</v>
       </c>
       <c r="S47" t="n">
         <v>13</v>
@@ -16298,7 +18646,7 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0.013501</v>
+        <v>0.00812</v>
       </c>
     </row>
     <row r="48">
@@ -16318,7 +18666,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -16348,19 +18696,19 @@
         <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0.006667</v>
+        <v>0.008</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.001178</v>
+        <v>0.002197</v>
       </c>
       <c r="R48" t="n">
-        <v>0.036793</v>
+        <v>0.028695</v>
       </c>
       <c r="S48" t="n">
         <v>13</v>
@@ -16369,7 +18717,7 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0.006834</v>
+        <v>0.008479</v>
       </c>
     </row>
     <row r="49">
@@ -16389,7 +18737,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -16419,19 +18767,19 @@
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>0.97503</v>
+        <v>0.984867</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>0.013333</v>
+        <v>0.008</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.003664</v>
+        <v>0.002197</v>
       </c>
       <c r="R49" t="n">
-        <v>0.047307</v>
+        <v>0.028695</v>
       </c>
       <c r="S49" t="n">
         <v>13</v>
@@ -16440,7 +18788,7 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0.014004</v>
+        <v>0.008957</v>
       </c>
     </row>
     <row r="50">
@@ -16460,58 +18808,58 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E50" t="n">
-        <v>0.99625</v>
+        <v>0.99775</v>
       </c>
       <c r="F50" t="n">
-        <v>0.036371</v>
+        <v>0.028196</v>
       </c>
       <c r="G50" t="n">
-        <v>0.00297</v>
+        <v>0.001783</v>
       </c>
       <c r="H50" t="n">
-        <v>0.990429</v>
+        <v>0.994255</v>
       </c>
       <c r="I50" t="n">
-        <v>1.002071</v>
+        <v>1.001245</v>
       </c>
       <c r="J50" t="n">
-        <v>0.997844</v>
+        <v>0.998712</v>
       </c>
       <c r="K50" t="n">
-        <v>0.992667</v>
+        <v>0.995752</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0.993333</v>
+        <v>0.996</v>
       </c>
       <c r="N50" t="n">
-        <v>0.963207</v>
+        <v>0.977694</v>
       </c>
       <c r="O50" t="n">
-        <v>0.998822</v>
+        <v>0.999294</v>
       </c>
       <c r="P50" t="n">
-        <v>0.013333</v>
+        <v>0.016</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.003664</v>
+        <v>0.006239</v>
       </c>
       <c r="R50" t="n">
-        <v>0.047307</v>
+        <v>0.04041</v>
       </c>
       <c r="S50" t="n">
         <v>13</v>
       </c>
       <c r="T50" t="n">
-        <v>0.993333</v>
+        <v>0.996</v>
       </c>
       <c r="U50" t="n">
-        <v>0.014004</v>
+        <v>0.016838</v>
       </c>
     </row>
     <row r="51">
@@ -16531,58 +18879,58 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5325</v>
+        <v>0.5277500000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>0.118479</v>
+        <v>0.12219</v>
       </c>
       <c r="G51" t="n">
-        <v>0.009674</v>
+        <v>0.007728</v>
       </c>
       <c r="H51" t="n">
-        <v>0.51354</v>
+        <v>0.5126039999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>0.55146</v>
+        <v>0.542896</v>
       </c>
       <c r="J51" t="n">
-        <v>0.579956</v>
+        <v>0.558424</v>
       </c>
       <c r="K51" t="n">
-        <v>0.513798</v>
+        <v>0.506441</v>
       </c>
       <c r="L51" t="n">
-        <v>0.6444260000000001</v>
+        <v>0.6120100000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>0.006667</v>
+        <v>0.012</v>
       </c>
       <c r="N51" t="n">
-        <v>0.001178</v>
+        <v>0.004089</v>
       </c>
       <c r="O51" t="n">
-        <v>0.036793</v>
+        <v>0.034681</v>
       </c>
       <c r="P51" t="n">
-        <v>0.013333</v>
+        <v>0.012</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.003664</v>
+        <v>0.004089</v>
       </c>
       <c r="R51" t="n">
-        <v>0.047307</v>
+        <v>0.034681</v>
       </c>
       <c r="S51" t="n">
         <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>0.008512</v>
+        <v>0.013915</v>
       </c>
       <c r="U51" t="n">
-        <v>0.014172</v>
+        <v>0.013316</v>
       </c>
     </row>
     <row r="52">
@@ -16602,7 +18950,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -16632,19 +18980,19 @@
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>0.005</v>
+        <v>0.003333</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.000883</v>
+        <v>0.000589</v>
       </c>
       <c r="R52" t="n">
-        <v>0.027774</v>
+        <v>0.018637</v>
       </c>
       <c r="S52" t="n">
         <v>13</v>
@@ -16653,7 +19001,7 @@
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>0.005629</v>
+        <v>0.004031</v>
       </c>
     </row>
     <row r="53">
@@ -16673,7 +19021,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -16703,19 +19051,19 @@
         <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.005114</v>
+        <v>0.003407</v>
       </c>
       <c r="R53" t="n">
-        <v>0.043166</v>
+        <v>0.028983</v>
       </c>
       <c r="S53" t="n">
         <v>13</v>
@@ -16724,7 +19072,7 @@
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>0.015252</v>
+        <v>0.010499</v>
       </c>
     </row>
     <row r="54">
@@ -16744,58 +19092,58 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E54" t="n">
-        <v>0.815625</v>
+        <v>0.814792</v>
       </c>
       <c r="F54" t="n">
-        <v>0.102717</v>
+        <v>0.108229</v>
       </c>
       <c r="G54" t="n">
-        <v>0.007263</v>
+        <v>0.006249</v>
       </c>
       <c r="H54" t="n">
-        <v>0.801389</v>
+        <v>0.802545</v>
       </c>
       <c r="I54" t="n">
-        <v>0.829861</v>
+        <v>0.827039</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9779870000000001</v>
+        <v>0.974456</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9665820000000001</v>
+        <v>0.964239</v>
       </c>
       <c r="L54" t="n">
-        <v>0.987726</v>
+        <v>0.983145</v>
       </c>
       <c r="M54" t="n">
-        <v>0.655</v>
+        <v>0.656667</v>
       </c>
       <c r="N54" t="n">
-        <v>0.5867560000000001</v>
+        <v>0.60126</v>
       </c>
       <c r="O54" t="n">
-        <v>0.717402</v>
+        <v>0.708112</v>
       </c>
       <c r="P54" t="n">
-        <v>0.005</v>
+        <v>0.006667</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.000883</v>
+        <v>0.00183</v>
       </c>
       <c r="R54" t="n">
-        <v>0.027774</v>
+        <v>0.023978</v>
       </c>
       <c r="S54" t="n">
         <v>13</v>
       </c>
       <c r="T54" t="n">
-        <v>0.659403</v>
+        <v>0.661752</v>
       </c>
       <c r="U54" t="n">
-        <v>0.005503</v>
+        <v>0.007165</v>
       </c>
     </row>
     <row r="55">
@@ -16815,7 +19163,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -16845,19 +19193,19 @@
         <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01</v>
+        <v>0.006667</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.002747</v>
+        <v>0.00183</v>
       </c>
       <c r="R55" t="n">
-        <v>0.035722</v>
+        <v>0.023978</v>
       </c>
       <c r="S55" t="n">
         <v>13</v>
@@ -16866,7 +19214,7 @@
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>0.010755</v>
+        <v>0.007365</v>
       </c>
     </row>
     <row r="56">
@@ -16886,7 +19234,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -16916,19 +19264,19 @@
         <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
       </c>
       <c r="P56" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.005114</v>
+        <v>0.003407</v>
       </c>
       <c r="R56" t="n">
-        <v>0.043166</v>
+        <v>0.028983</v>
       </c>
       <c r="S56" t="n">
         <v>13</v>
@@ -16937,7 +19285,7 @@
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>0.015503</v>
+        <v>0.010798</v>
       </c>
     </row>
     <row r="57">
@@ -16957,7 +19305,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -16987,19 +19335,19 @@
         <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>0.003333</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>0.000589</v>
       </c>
       <c r="R57" t="n">
-        <v>0.018845</v>
+        <v>0.018637</v>
       </c>
       <c r="S57" t="n">
         <v>13</v>
@@ -17008,7 +19356,7 @@
         <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>0.000629</v>
+        <v>0.004231</v>
       </c>
     </row>
     <row r="58">
@@ -17028,7 +19376,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -17058,19 +19406,19 @@
         <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>0.005</v>
+        <v>0.003333</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.000883</v>
+        <v>0.000589</v>
       </c>
       <c r="R58" t="n">
-        <v>0.027774</v>
+        <v>0.018637</v>
       </c>
       <c r="S58" t="n">
         <v>13</v>
@@ -17079,7 +19427,7 @@
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>0.005629</v>
+        <v>0.004031</v>
       </c>
     </row>
     <row r="59">
@@ -17099,7 +19447,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -17129,19 +19477,19 @@
         <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="O59" t="n">
         <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>0.01</v>
+        <v>0.006667</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.002747</v>
+        <v>0.00183</v>
       </c>
       <c r="R59" t="n">
-        <v>0.035722</v>
+        <v>0.023978</v>
       </c>
       <c r="S59" t="n">
         <v>13</v>
@@ -17150,7 +19498,7 @@
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>0.010755</v>
+        <v>0.007365</v>
       </c>
     </row>
     <row r="60">
@@ -17170,7 +19518,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -17200,19 +19548,19 @@
         <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>0.981155</v>
+        <v>0.987357</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>0.005</v>
+        <v>0.003333</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.000883</v>
+        <v>0.000589</v>
       </c>
       <c r="R60" t="n">
-        <v>0.027774</v>
+        <v>0.018637</v>
       </c>
       <c r="S60" t="n">
         <v>13</v>
@@ -17221,7 +19569,7 @@
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>0.006635</v>
+        <v>0.004829</v>
       </c>
     </row>
     <row r="61">
@@ -17241,58 +19589,58 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E61" t="n">
-        <v>0.537188</v>
+        <v>0.530625</v>
       </c>
       <c r="F61" t="n">
-        <v>0.129033</v>
+        <v>0.128248</v>
       </c>
       <c r="G61" t="n">
-        <v>0.009124</v>
+        <v>0.007404</v>
       </c>
       <c r="H61" t="n">
-        <v>0.519305</v>
+        <v>0.516113</v>
       </c>
       <c r="I61" t="n">
-        <v>0.55507</v>
+        <v>0.545137</v>
       </c>
       <c r="J61" t="n">
-        <v>0.56525</v>
+        <v>0.564411</v>
       </c>
       <c r="K61" t="n">
-        <v>0.51131</v>
+        <v>0.517215</v>
       </c>
       <c r="L61" t="n">
-        <v>0.620413</v>
+        <v>0.610098</v>
       </c>
       <c r="M61" t="n">
         <v>0.03</v>
       </c>
       <c r="N61" t="n">
-        <v>0.01382</v>
+        <v>0.015862</v>
       </c>
       <c r="O61" t="n">
-        <v>0.06389400000000001</v>
+        <v>0.056023</v>
       </c>
       <c r="P61" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.000883</v>
+        <v>0.003407</v>
       </c>
       <c r="R61" t="n">
-        <v>0.027774</v>
+        <v>0.028983</v>
       </c>
       <c r="S61" t="n">
         <v>13</v>
       </c>
       <c r="T61" t="n">
-        <v>0.030881</v>
+        <v>0.030997</v>
       </c>
       <c r="U61" t="n">
-        <v>0.006006</v>
+        <v>0.010897</v>
       </c>
     </row>
     <row r="62">
@@ -17312,7 +19660,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -17342,19 +19690,19 @@
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="O62" t="n">
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.004089</v>
+        <v>0.006892</v>
       </c>
       <c r="R62" t="n">
-        <v>0.034681</v>
+        <v>0.032335</v>
       </c>
       <c r="S62" t="n">
         <v>13</v>
@@ -17363,7 +19711,7 @@
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>0.012704</v>
+        <v>0.015524</v>
       </c>
     </row>
     <row r="63">
@@ -17383,7 +19731,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -17413,19 +19761,19 @@
         <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>0.004</v>
+        <v>0.0125</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.000706</v>
+        <v>0.005351</v>
       </c>
       <c r="R63" t="n">
-        <v>0.022306</v>
+        <v>0.028924</v>
       </c>
       <c r="S63" t="n">
         <v>13</v>
@@ -17434,7 +19782,7 @@
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>0.004704</v>
+        <v>0.013098</v>
       </c>
     </row>
     <row r="64">
@@ -17454,58 +19802,58 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E64" t="n">
-        <v>0.757</v>
+        <v>0.757969</v>
       </c>
       <c r="F64" t="n">
-        <v>0.131654</v>
+        <v>0.130386</v>
       </c>
       <c r="G64" t="n">
-        <v>0.008326999999999999</v>
+        <v>0.006519</v>
       </c>
       <c r="H64" t="n">
-        <v>0.74068</v>
+        <v>0.745191</v>
       </c>
       <c r="I64" t="n">
-        <v>0.77332</v>
+        <v>0.770746</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9302240000000001</v>
+        <v>0.925872</v>
       </c>
       <c r="K64" t="n">
-        <v>0.91047</v>
+        <v>0.908322</v>
       </c>
       <c r="L64" t="n">
-        <v>0.948041</v>
+        <v>0.941805</v>
       </c>
       <c r="M64" t="n">
-        <v>0.456</v>
+        <v>0.46</v>
       </c>
       <c r="N64" t="n">
-        <v>0.395392</v>
+        <v>0.41177</v>
       </c>
       <c r="O64" t="n">
-        <v>0.51794</v>
+        <v>0.508991</v>
       </c>
       <c r="P64" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.002197</v>
+        <v>0.003895</v>
       </c>
       <c r="R64" t="n">
-        <v>0.028695</v>
+        <v>0.025427</v>
       </c>
       <c r="S64" t="n">
         <v>13</v>
       </c>
       <c r="T64" t="n">
-        <v>0.460226</v>
+        <v>0.465235</v>
       </c>
       <c r="U64" t="n">
-        <v>0.008503</v>
+        <v>0.010524</v>
       </c>
     </row>
     <row r="65">
@@ -17525,7 +19873,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -17555,19 +19903,19 @@
         <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.004089</v>
+        <v>0.003895</v>
       </c>
       <c r="R65" t="n">
-        <v>0.034681</v>
+        <v>0.025427</v>
       </c>
       <c r="S65" t="n">
         <v>13</v>
@@ -17576,7 +19924,7 @@
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>0.012403</v>
+        <v>0.010598</v>
       </c>
     </row>
     <row r="66">
@@ -17596,7 +19944,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -17626,19 +19974,19 @@
         <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="O66" t="n">
         <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>0.008</v>
+        <v>0.0125</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.002197</v>
+        <v>0.005351</v>
       </c>
       <c r="R66" t="n">
-        <v>0.028695</v>
+        <v>0.028924</v>
       </c>
       <c r="S66" t="n">
         <v>13</v>
@@ -17647,7 +19995,7 @@
         <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>0.009006</v>
+        <v>0.013248</v>
       </c>
     </row>
     <row r="67">
@@ -17667,7 +20015,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
@@ -17697,19 +20045,19 @@
         <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.002197</v>
+        <v>0.001372</v>
       </c>
       <c r="R67" t="n">
-        <v>0.028695</v>
+        <v>0.018045</v>
       </c>
       <c r="S67" t="n">
         <v>13</v>
@@ -17718,7 +20066,7 @@
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0.008704</v>
+        <v>0.005897</v>
       </c>
     </row>
     <row r="68">
@@ -17738,7 +20086,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -17768,19 +20116,19 @@
         <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.004089</v>
+        <v>0.006892</v>
       </c>
       <c r="R68" t="n">
-        <v>0.034681</v>
+        <v>0.032335</v>
       </c>
       <c r="S68" t="n">
         <v>13</v>
@@ -17789,7 +20137,7 @@
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>0.012704</v>
+        <v>0.015524</v>
       </c>
     </row>
     <row r="69">
@@ -17809,7 +20157,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -17839,19 +20187,19 @@
         <v>1</v>
       </c>
       <c r="N69" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="O69" t="n">
         <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.006239</v>
+        <v>0.010168</v>
       </c>
       <c r="R69" t="n">
-        <v>0.04041</v>
+        <v>0.038963</v>
       </c>
       <c r="S69" t="n">
         <v>13</v>
@@ -17860,7 +20208,7 @@
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>0.016906</v>
+        <v>0.020748</v>
       </c>
     </row>
     <row r="70">
@@ -17880,22 +20228,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.998906</v>
       </c>
       <c r="F70" t="n">
-        <v>0.009585</v>
+        <v>0.008206</v>
       </c>
       <c r="G70" t="n">
-        <v>0.000606</v>
+        <v>0.00041</v>
       </c>
       <c r="H70" t="n">
-        <v>0.997312</v>
+        <v>0.998102</v>
       </c>
       <c r="I70" t="n">
-        <v>0.999688</v>
+        <v>0.99971</v>
       </c>
       <c r="J70" t="n">
         <v>1</v>
@@ -17910,19 +20258,19 @@
         <v>1</v>
       </c>
       <c r="N70" t="n">
-        <v>0.984867</v>
+        <v>0.990488</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>0.012</v>
+        <v>0.0075</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.004089</v>
+        <v>0.002554</v>
       </c>
       <c r="R70" t="n">
-        <v>0.034681</v>
+        <v>0.021816</v>
       </c>
       <c r="S70" t="n">
         <v>13</v>
@@ -17931,7 +20279,7 @@
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>0.012704</v>
+        <v>0.008397</v>
       </c>
     </row>
     <row r="71">
@@ -17951,40 +20299,40 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E71" t="n">
-        <v>0.523</v>
+        <v>0.524844</v>
       </c>
       <c r="F71" t="n">
-        <v>0.126009</v>
+        <v>0.123653</v>
       </c>
       <c r="G71" t="n">
-        <v>0.00797</v>
+        <v>0.006183</v>
       </c>
       <c r="H71" t="n">
-        <v>0.5073800000000001</v>
+        <v>0.512726</v>
       </c>
       <c r="I71" t="n">
-        <v>0.53862</v>
+        <v>0.5369620000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>0.543632</v>
+        <v>0.565069</v>
       </c>
       <c r="K71" t="n">
-        <v>0.488739</v>
+        <v>0.525227</v>
       </c>
       <c r="L71" t="n">
-        <v>0.594282</v>
+        <v>0.60487</v>
       </c>
       <c r="M71" t="n">
         <v>0.02</v>
       </c>
       <c r="N71" t="n">
-        <v>0.008572</v>
+        <v>0.010168</v>
       </c>
       <c r="O71" t="n">
-        <v>0.045956</v>
+        <v>0.038963</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -17993,16 +20341,16 @@
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.015133</v>
+        <v>0.009512</v>
       </c>
       <c r="S71" t="n">
         <v>13</v>
       </c>
       <c r="T71" t="n">
-        <v>0.021208</v>
+        <v>0.021496</v>
       </c>
       <c r="U71" t="n">
-        <v>0.000503</v>
+        <v>0.000673</v>
       </c>
     </row>
     <row r="72">
@@ -20203,7 +22551,7 @@
         <v>1</v>
       </c>
       <c r="U102" t="n">
-        <v>0.011891</v>
+        <v>0.010995</v>
       </c>
     </row>
     <row r="103">
@@ -20274,7 +22622,7 @@
         <v>1</v>
       </c>
       <c r="U103" t="n">
-        <v>0.019649</v>
+        <v>0.018631</v>
       </c>
     </row>
     <row r="104">
@@ -20342,10 +22690,10 @@
         <v>9</v>
       </c>
       <c r="T104" t="n">
-        <v>0.717658</v>
+        <v>0.715215</v>
       </c>
       <c r="U104" t="n">
-        <v>0.009305000000000001</v>
+        <v>0.008449999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -20416,7 +22764,7 @@
         <v>1</v>
       </c>
       <c r="U105" t="n">
-        <v>0.021633</v>
+        <v>0.02086</v>
       </c>
     </row>
     <row r="106">
@@ -20487,7 +22835,7 @@
         <v>1</v>
       </c>
       <c r="U106" t="n">
-        <v>0.011805</v>
+        <v>0.01095</v>
       </c>
     </row>
     <row r="107">
@@ -20558,7 +22906,7 @@
         <v>1</v>
       </c>
       <c r="U107" t="n">
-        <v>0.011633</v>
+        <v>0.01086</v>
       </c>
     </row>
     <row r="108">
@@ -20629,7 +22977,7 @@
         <v>1</v>
       </c>
       <c r="U108" t="n">
-        <v>0.011891</v>
+        <v>0.010995</v>
       </c>
     </row>
     <row r="109">
@@ -20700,7 +23048,7 @@
         <v>1</v>
       </c>
       <c r="U109" t="n">
-        <v>0.012063</v>
+        <v>0.011086</v>
       </c>
     </row>
     <row r="110">
@@ -20768,10 +23116,10 @@
         <v>9</v>
       </c>
       <c r="T110" t="n">
-        <v>0.987586</v>
+        <v>0.987545</v>
       </c>
       <c r="U110" t="n">
-        <v>0.013789</v>
+        <v>0.013179</v>
       </c>
     </row>
     <row r="111">
@@ -20839,10 +23187,10 @@
         <v>9</v>
       </c>
       <c r="T111" t="n">
-        <v>0.360315</v>
+        <v>0.35543</v>
       </c>
       <c r="U111" t="n">
-        <v>0.011805</v>
+        <v>0.01095</v>
       </c>
     </row>
     <row r="112">
@@ -20862,7 +23210,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -20892,19 +23240,19 @@
         <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="O112" t="n">
         <v>1</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>0.001702</v>
       </c>
       <c r="R112" t="n">
-        <v>0.009512</v>
+        <v>0.014596</v>
       </c>
       <c r="S112" t="n">
         <v>9</v>
@@ -20913,7 +23261,7 @@
         <v>1</v>
       </c>
       <c r="U112" t="n">
-        <v>0.001032</v>
+        <v>0.005724</v>
       </c>
     </row>
     <row r="113">
@@ -20933,7 +23281,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
@@ -20963,19 +23311,19 @@
         <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
       </c>
       <c r="P113" t="n">
-        <v>0.0075</v>
+        <v>0.006667</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.002554</v>
+        <v>0.002596</v>
       </c>
       <c r="R113" t="n">
-        <v>0.021816</v>
+        <v>0.017015</v>
       </c>
       <c r="S113" t="n">
         <v>9</v>
@@ -20984,7 +23332,7 @@
         <v>1</v>
       </c>
       <c r="U113" t="n">
-        <v>0.008274</v>
+        <v>0.00727</v>
       </c>
     </row>
     <row r="114">
@@ -21004,58 +23352,58 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E114" t="n">
-        <v>0.89125</v>
+        <v>0.893</v>
       </c>
       <c r="F114" t="n">
-        <v>0.116328</v>
+        <v>0.110626</v>
       </c>
       <c r="G114" t="n">
-        <v>0.005816</v>
+        <v>0.004516</v>
       </c>
       <c r="H114" t="n">
-        <v>0.87985</v>
+        <v>0.884148</v>
       </c>
       <c r="I114" t="n">
-        <v>0.90265</v>
+        <v>0.901852</v>
       </c>
       <c r="J114" t="n">
-        <v>0.969834</v>
+        <v>0.973268</v>
       </c>
       <c r="K114" t="n">
-        <v>0.959646</v>
+        <v>0.965524</v>
       </c>
       <c r="L114" t="n">
-        <v>0.979166</v>
+        <v>0.980824</v>
       </c>
       <c r="M114" t="n">
-        <v>0.725</v>
+        <v>0.726667</v>
       </c>
       <c r="N114" t="n">
-        <v>0.679258</v>
+        <v>0.689649</v>
       </c>
       <c r="O114" t="n">
-        <v>0.7664609999999999</v>
+        <v>0.7608009999999999</v>
       </c>
       <c r="P114" t="n">
-        <v>0.005</v>
+        <v>0.006667</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.001372</v>
+        <v>0.002596</v>
       </c>
       <c r="R114" t="n">
-        <v>0.018045</v>
+        <v>0.017015</v>
       </c>
       <c r="S114" t="n">
         <v>9</v>
       </c>
       <c r="T114" t="n">
-        <v>0.730244</v>
+        <v>0.729623</v>
       </c>
       <c r="U114" t="n">
-        <v>0.006547</v>
+        <v>0.007421</v>
       </c>
     </row>
     <row r="115">
@@ -21075,7 +23423,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
@@ -21105,19 +23453,19 @@
         <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="O115" t="n">
         <v>1</v>
       </c>
       <c r="P115" t="n">
-        <v>0.005</v>
+        <v>0.008333</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.001372</v>
+        <v>0.003565</v>
       </c>
       <c r="R115" t="n">
-        <v>0.018045</v>
+        <v>0.019358</v>
       </c>
       <c r="S115" t="n">
         <v>9</v>
@@ -21126,7 +23474,7 @@
         <v>1</v>
       </c>
       <c r="U115" t="n">
-        <v>0.006117</v>
+        <v>0.009117999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -21146,7 +23494,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -21164,10 +23512,10 @@
         <v>1</v>
       </c>
       <c r="J116" t="n">
-        <v>0.99875</v>
+        <v>0.999167</v>
       </c>
       <c r="K116" t="n">
-        <v>0.99625</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -21176,19 +23524,19 @@
         <v>1</v>
       </c>
       <c r="N116" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="O116" t="n">
         <v>1</v>
       </c>
       <c r="P116" t="n">
-        <v>0.0025</v>
+        <v>0.003333</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.000441</v>
+        <v>0.000915</v>
       </c>
       <c r="R116" t="n">
-        <v>0.014023</v>
+        <v>0.012071</v>
       </c>
       <c r="S116" t="n">
         <v>9</v>
@@ -21197,7 +23545,7 @@
         <v>1</v>
       </c>
       <c r="U116" t="n">
-        <v>0.003703</v>
+        <v>0.004027</v>
       </c>
     </row>
     <row r="117">
@@ -21217,7 +23565,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E117" t="n">
         <v>1</v>
@@ -21247,19 +23595,19 @@
         <v>1</v>
       </c>
       <c r="N117" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="O117" t="n">
         <v>1</v>
       </c>
       <c r="P117" t="n">
-        <v>0.005</v>
+        <v>0.006667</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.001372</v>
+        <v>0.002596</v>
       </c>
       <c r="R117" t="n">
-        <v>0.018045</v>
+        <v>0.017015</v>
       </c>
       <c r="S117" t="n">
         <v>9</v>
@@ -21268,7 +23616,7 @@
         <v>1</v>
       </c>
       <c r="U117" t="n">
-        <v>0.005946</v>
+        <v>0.007179</v>
       </c>
     </row>
     <row r="118">
@@ -21288,7 +23636,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E118" t="n">
         <v>1</v>
@@ -21318,19 +23666,19 @@
         <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="O118" t="n">
         <v>1</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>0.001702</v>
       </c>
       <c r="R118" t="n">
-        <v>0.009512</v>
+        <v>0.014596</v>
       </c>
       <c r="S118" t="n">
         <v>9</v>
@@ -21339,7 +23687,7 @@
         <v>1</v>
       </c>
       <c r="U118" t="n">
-        <v>0.000946</v>
+        <v>0.005694</v>
       </c>
     </row>
     <row r="119">
@@ -21359,7 +23707,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -21377,10 +23725,10 @@
         <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0.999167</v>
       </c>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
@@ -21389,19 +23737,19 @@
         <v>1</v>
       </c>
       <c r="N119" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="O119" t="n">
         <v>1</v>
       </c>
       <c r="P119" t="n">
-        <v>0.005</v>
+        <v>0.006667</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.001372</v>
+        <v>0.002596</v>
       </c>
       <c r="R119" t="n">
-        <v>0.018045</v>
+        <v>0.017015</v>
       </c>
       <c r="S119" t="n">
         <v>9</v>
@@ -21410,7 +23758,7 @@
         <v>1</v>
       </c>
       <c r="U119" t="n">
-        <v>0.006289</v>
+        <v>0.00736</v>
       </c>
     </row>
     <row r="120">
@@ -21430,7 +23778,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -21448,10 +23796,10 @@
         <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>0.999167</v>
       </c>
       <c r="K120" t="n">
-        <v>1</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="L120" t="n">
         <v>1</v>
@@ -21460,19 +23808,19 @@
         <v>1</v>
       </c>
       <c r="N120" t="n">
-        <v>0.990488</v>
+        <v>0.993638</v>
       </c>
       <c r="O120" t="n">
         <v>1</v>
       </c>
       <c r="P120" t="n">
-        <v>0.0125</v>
+        <v>0.011667</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.005351</v>
+        <v>0.005663</v>
       </c>
       <c r="R120" t="n">
-        <v>0.028924</v>
+        <v>0.023884</v>
       </c>
       <c r="S120" t="n">
         <v>9</v>
@@ -21481,7 +23829,7 @@
         <v>1</v>
       </c>
       <c r="U120" t="n">
-        <v>0.013703</v>
+        <v>0.01224</v>
       </c>
     </row>
     <row r="121">
@@ -21501,58 +23849,1478 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E121" t="n">
-        <v>0.76475</v>
+        <v>0.7715</v>
       </c>
       <c r="F121" t="n">
-        <v>0.129322</v>
+        <v>0.125953</v>
       </c>
       <c r="G121" t="n">
-        <v>0.006466</v>
+        <v>0.005142</v>
       </c>
       <c r="H121" t="n">
-        <v>0.752077</v>
+        <v>0.761422</v>
       </c>
       <c r="I121" t="n">
-        <v>0.777423</v>
+        <v>0.781578</v>
       </c>
       <c r="J121" t="n">
-        <v>0.892753</v>
+        <v>0.897576</v>
       </c>
       <c r="K121" t="n">
-        <v>0.871702</v>
+        <v>0.879615</v>
       </c>
       <c r="L121" t="n">
-        <v>0.912431</v>
+        <v>0.913436</v>
       </c>
       <c r="M121" t="n">
-        <v>0.2725</v>
+        <v>0.29</v>
       </c>
       <c r="N121" t="n">
-        <v>0.231185</v>
+        <v>0.255119</v>
       </c>
       <c r="O121" t="n">
-        <v>0.318143</v>
+        <v>0.327553</v>
       </c>
       <c r="P121" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.003895</v>
+        <v>0.007911</v>
       </c>
       <c r="R121" t="n">
-        <v>0.025427</v>
+        <v>0.02826</v>
       </c>
       <c r="S121" t="n">
         <v>9</v>
       </c>
       <c r="T121" t="n">
-        <v>0.282213</v>
+        <v>0.295279</v>
       </c>
       <c r="U121" t="n">
-        <v>0.011977</v>
+        <v>0.015995</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>LibriSpeech-dev</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>No Distortion</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>50</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" t="n">
+        <v>1</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S122" t="n">
+        <v>26</v>
+      </c>
+      <c r="T122" t="n">
+        <v>1</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>LibriSpeech-dev</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Resample (8k)</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>50</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9065</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.181744</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.025702</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.856124</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.9568759999999999</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.9184</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.8596</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.9676</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.714858</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.9166260000000001</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>26</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>LibriSpeech-dev</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Gaussian Noise</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>50</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.046991</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.006646</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.480975</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5070249999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4994</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.402785</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.6018250000000001</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.011039</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.134601</v>
+      </c>
+      <c r="S124" t="n">
+        <v>26</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>LibriSpeech-dev</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Median Filter</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>50</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9915</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.007057</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.977669</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1.005331</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="S125" t="n">
+        <v>26</v>
+      </c>
+      <c r="T125" t="n">
+        <v>1</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>LibriSpeech-dev</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Low-pass 4k</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>50</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.119439</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.016891</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.9283940000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.994606</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.9718</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.9342</v>
+      </c>
+      <c r="L126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.837829</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.979385</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="S126" t="n">
+        <v>26</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>LibriSpeech-dev</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>High-pass 500</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>50</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.09980700000000001</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.014115</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.947835</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1.003165</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.865399</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.988961</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.011039</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.134601</v>
+      </c>
+      <c r="S127" t="n">
+        <v>26</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>LibriSpeech-dev</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Reencode</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>50</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S128" t="n">
+        <v>26</v>
+      </c>
+      <c r="T128" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>LibriSpeech-dev</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Compression</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>50</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S129" t="n">
+        <v>26</v>
+      </c>
+      <c r="T129" t="n">
+        <v>1</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>LibriSpeech-dev</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Noise Suppression</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>50</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.186589</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.026388</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.8392810000000001</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.942719</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.8539949999999999</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.965605</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.692039</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.902298</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S130" t="n">
+        <v>26</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>LibriSpeech-dev</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Phone Call</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>50</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.033308</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.00471</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.490268</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.508732</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.4908</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.422995</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.564405</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="S131" t="n">
+        <v>26</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>LJSpeech</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>No Distortion</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>50</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S132" t="n">
+        <v>26</v>
+      </c>
+      <c r="T132" t="n">
+        <v>1</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>LJSpeech</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Resample (8k)</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>50</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.9115</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.188996</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.026728</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.859114</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.963886</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.9214</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.858985</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.97061</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.714858</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.9166260000000001</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S133" t="n">
+        <v>26</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>LJSpeech</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Gaussian Noise</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>50</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.043825</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.006198</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.482352</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.506648</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.360995</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.548005</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.011039</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.134601</v>
+      </c>
+      <c r="S134" t="n">
+        <v>26</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>LJSpeech</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Median Filter</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>50</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.092029</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.013015</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.959491</v>
+      </c>
+      <c r="I135" t="n">
+        <v>1.010509</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.895046</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.996461</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S135" t="n">
+        <v>26</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>LJSpeech</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Low-pass 4k</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>50</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.159652</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.022578</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.894748</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.983252</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.9424</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.8943950000000001</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.985605</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.761952</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.943824</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.104954</v>
+      </c>
+      <c r="S136" t="n">
+        <v>26</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>LJSpeech</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>High-pass 500</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>50</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.9785</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.09897599999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.013997</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.951066</v>
+      </c>
+      <c r="I137" t="n">
+        <v>1.005934</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.9792</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.865399</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.988961</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S137" t="n">
+        <v>26</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>LJSpeech</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Reencode</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>50</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>26</v>
+      </c>
+      <c r="T138" t="n">
+        <v>1</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>LJSpeech</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Compression</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>50</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1</v>
+      </c>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.928652</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S139" t="n">
+        <v>26</v>
+      </c>
+      <c r="T139" t="n">
+        <v>1</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>LJSpeech</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Noise Suppression</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>50</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.151514</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.021427</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.8985030000000001</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.982497</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.9452</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.88878</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.9882</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.786398</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.956524</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S140" t="n">
+        <v>26</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SilentCipher</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>LJSpeech</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Phone Call</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>50</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.036365</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.005143</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.48792</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.50808</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.4482</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.592005</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.07134799999999999</v>
+      </c>
+      <c r="S141" t="n">
+        <v>26</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/watermarking_model/results/evals/detection_metrics.xlsx
+++ b/watermarking_model/results/evals/detection_metrics.xlsx
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7049</v>
+        <v>8625</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -2003,7 +2003,7 @@
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.999455</v>
+        <v>0.999555</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.000545</v>
+        <v>0.000445</v>
       </c>
       <c r="Q31" t="n">
         <v>9</v>
@@ -2024,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="32">
@@ -2034,22 +2034,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7049</v>
+        <v>8625</v>
       </c>
       <c r="C32" t="n">
         <v>0.99999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.000744</v>
+        <v>0.000673</v>
       </c>
       <c r="E32" t="n">
-        <v>9e-06</v>
+        <v>7e-06</v>
       </c>
       <c r="F32" t="n">
-        <v>0.999974</v>
+        <v>0.999979</v>
       </c>
       <c r="G32" t="n">
-        <v>1.000009</v>
+        <v>1.000007</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -2064,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.999455</v>
+        <v>0.999555</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.000545</v>
+        <v>0.000445</v>
       </c>
       <c r="Q32" t="n">
         <v>9</v>
@@ -2085,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="33">
@@ -2095,58 +2095,58 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7049</v>
+        <v>8625</v>
       </c>
       <c r="C33" t="n">
-        <v>0.500177</v>
+        <v>0.500207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.007255</v>
+        <v>0.009127</v>
       </c>
       <c r="E33" t="n">
-        <v>8.6e-05</v>
+        <v>9.8e-05</v>
       </c>
       <c r="F33" t="n">
-        <v>0.499981</v>
+        <v>0.5000250000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.50032</v>
+        <v>0.50041</v>
       </c>
       <c r="H33" t="n">
-        <v>0.50045</v>
+        <v>0.500396</v>
       </c>
       <c r="I33" t="n">
-        <v>0.500142</v>
+        <v>0.500116</v>
       </c>
       <c r="J33" t="n">
-        <v>0.50078</v>
+        <v>0.500753</v>
       </c>
       <c r="K33" t="n">
-        <v>0.000651</v>
+        <v>0.000668</v>
       </c>
       <c r="L33" t="n">
-        <v>0.000221</v>
+        <v>0.000319</v>
       </c>
       <c r="M33" t="n">
-        <v>0.001458</v>
+        <v>0.001517</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>9.3e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>0.000545</v>
+        <v>0.000657</v>
       </c>
       <c r="Q33" t="n">
         <v>9</v>
       </c>
       <c r="R33" t="n">
-        <v>0.010644</v>
+        <v>0.01065</v>
       </c>
       <c r="S33" t="n">
-        <v>0.009998</v>
+        <v>0.010078</v>
       </c>
     </row>
     <row r="34">
@@ -2156,40 +2156,40 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>7049</v>
+        <v>8625</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9993</v>
+        <v>0.99917</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01228</v>
+        <v>0.013832</v>
       </c>
       <c r="E34" t="n">
-        <v>0.000146</v>
+        <v>0.000149</v>
       </c>
       <c r="F34" t="n">
-        <v>0.998995</v>
+        <v>0.998853</v>
       </c>
       <c r="G34" t="n">
-        <v>0.999568</v>
+        <v>0.999437</v>
       </c>
       <c r="H34" t="n">
-        <v>0.999798</v>
+        <v>0.999722</v>
       </c>
       <c r="I34" t="n">
-        <v>0.999503</v>
+        <v>0.99942</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0.999942</v>
       </c>
       <c r="K34" t="n">
-        <v>0.999596</v>
+        <v>0.999443</v>
       </c>
       <c r="L34" t="n">
-        <v>0.998749</v>
+        <v>0.998644</v>
       </c>
       <c r="M34" t="n">
-        <v>0.999855</v>
+        <v>0.999752</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2198,16 +2198,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.000545</v>
+        <v>0.000445</v>
       </c>
       <c r="Q34" t="n">
         <v>9</v>
       </c>
       <c r="R34" t="n">
-        <v>0.9996</v>
+        <v>0.999449</v>
       </c>
       <c r="S34" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="35">
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>7049</v>
+        <v>8625</v>
       </c>
       <c r="C35" t="n">
         <v>0.99999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.000744</v>
+        <v>0.000673</v>
       </c>
       <c r="E35" t="n">
-        <v>9e-06</v>
+        <v>7e-06</v>
       </c>
       <c r="F35" t="n">
-        <v>0.999974</v>
+        <v>0.999979</v>
       </c>
       <c r="G35" t="n">
-        <v>1.000009</v>
+        <v>1.000007</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -2247,7 +2247,7 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.999455</v>
+        <v>0.999555</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.000545</v>
+        <v>0.000445</v>
       </c>
       <c r="Q35" t="n">
         <v>9</v>
@@ -2268,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="36">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7049</v>
+        <v>8625</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -2308,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.999455</v>
+        <v>0.999555</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.000545</v>
+        <v>0.000445</v>
       </c>
       <c r="Q36" t="n">
         <v>9</v>
@@ -2329,7 +2329,7 @@
         <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="37">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>7049</v>
+        <v>8625</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -2369,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0.999455</v>
+        <v>0.999555</v>
       </c>
       <c r="M37" t="n">
         <v>1</v>
@@ -2381,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.000545</v>
+        <v>0.000445</v>
       </c>
       <c r="Q37" t="n">
         <v>9</v>
@@ -2390,7 +2390,7 @@
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="38">
@@ -2400,22 +2400,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7049</v>
+        <v>8625</v>
       </c>
       <c r="C38" t="n">
         <v>0.99999</v>
       </c>
       <c r="D38" t="n">
-        <v>0.000744</v>
+        <v>0.000673</v>
       </c>
       <c r="E38" t="n">
-        <v>9e-06</v>
+        <v>7e-06</v>
       </c>
       <c r="F38" t="n">
-        <v>0.999974</v>
+        <v>0.999979</v>
       </c>
       <c r="G38" t="n">
-        <v>1.000009</v>
+        <v>1.000007</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.999455</v>
+        <v>0.999555</v>
       </c>
       <c r="M38" t="n">
         <v>1</v>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.000545</v>
+        <v>0.000445</v>
       </c>
       <c r="Q38" t="n">
         <v>9</v>
@@ -2451,7 +2451,7 @@
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="39">
@@ -2461,40 +2461,40 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7049</v>
+        <v>8625</v>
       </c>
       <c r="C39" t="n">
-        <v>0.977413</v>
+        <v>0.978101</v>
       </c>
       <c r="D39" t="n">
-        <v>0.097176</v>
+        <v>0.093935</v>
       </c>
       <c r="E39" t="n">
-        <v>0.001157</v>
+        <v>0.001011</v>
       </c>
       <c r="F39" t="n">
-        <v>0.975955</v>
+        <v>0.977648</v>
       </c>
       <c r="G39" t="n">
-        <v>0.980492</v>
+        <v>0.981613</v>
       </c>
       <c r="H39" t="n">
-        <v>0.979889</v>
+        <v>0.980599</v>
       </c>
       <c r="I39" t="n">
-        <v>0.978366</v>
+        <v>0.98</v>
       </c>
       <c r="J39" t="n">
-        <v>0.982834</v>
+        <v>0.983884</v>
       </c>
       <c r="K39" t="n">
-        <v>0.959778</v>
+        <v>0.961198</v>
       </c>
       <c r="L39" t="n">
-        <v>0.95651</v>
+        <v>0.959796</v>
       </c>
       <c r="M39" t="n">
-        <v>0.96553</v>
+        <v>0.967675</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -2503,16 +2503,16 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.000545</v>
+        <v>0.000445</v>
       </c>
       <c r="Q39" t="n">
         <v>9</v>
       </c>
       <c r="R39" t="n">
-        <v>0.960181</v>
+        <v>0.9615860000000001</v>
       </c>
       <c r="S39" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="40">
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7049</v>
+        <v>8625</v>
       </c>
       <c r="C40" t="n">
         <v>0.5</v>
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.000545</v>
+        <v>0.000445</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -2564,16 +2564,16 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.000545</v>
+        <v>0.000445</v>
       </c>
       <c r="Q40" t="n">
         <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="S40" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="42">
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -5594,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="Q31" t="n">
         <v>9</v>
@@ -5615,7 +5615,7 @@
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="32">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -5655,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="Q32" t="n">
         <v>9</v>
@@ -5676,7 +5676,7 @@
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="33">
@@ -5686,40 +5686,40 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="C33" t="n">
-        <v>0.500613</v>
+        <v>0.500733</v>
       </c>
       <c r="D33" t="n">
-        <v>0.015336</v>
+        <v>0.017217</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000406</v>
+        <v>0.000359</v>
       </c>
       <c r="F33" t="n">
-        <v>0.499817</v>
+        <v>0.50003</v>
       </c>
       <c r="G33" t="n">
-        <v>0.501409</v>
+        <v>0.501436</v>
       </c>
       <c r="H33" t="n">
-        <v>0.501051</v>
+        <v>0.501086</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.500217</v>
       </c>
       <c r="J33" t="n">
-        <v>0.502453</v>
+        <v>0.502171</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002102</v>
+        <v>0.002171</v>
       </c>
       <c r="L33" t="n">
-        <v>0.000715</v>
+        <v>0.000928</v>
       </c>
       <c r="M33" t="n">
-        <v>0.006163</v>
+        <v>0.005072</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -5728,16 +5728,16 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="Q33" t="n">
         <v>9</v>
       </c>
       <c r="R33" t="n">
-        <v>0.012082</v>
+        <v>0.012138</v>
       </c>
       <c r="S33" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="34">
@@ -5747,22 +5747,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="C34" t="n">
-        <v>0.99965</v>
+        <v>0.99962</v>
       </c>
       <c r="D34" t="n">
-        <v>0.005222</v>
+        <v>0.005197</v>
       </c>
       <c r="E34" t="n">
-        <v>0.000138</v>
+        <v>0.000108</v>
       </c>
       <c r="F34" t="n">
-        <v>0.999379</v>
+        <v>0.999408</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9999209999999999</v>
+        <v>0.9998320000000001</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
@@ -5777,7 +5777,7 @@
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="M34" t="n">
         <v>1</v>
@@ -5789,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="Q34" t="n">
         <v>9</v>
@@ -5798,7 +5798,7 @@
         <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="35">
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -5838,7 +5838,7 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>
@@ -5850,7 +5850,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="Q35" t="n">
         <v>9</v>
@@ -5859,7 +5859,7 @@
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="36">
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
@@ -5911,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="Q36" t="n">
         <v>9</v>
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="37">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -5960,7 +5960,7 @@
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="M37" t="n">
         <v>1</v>
@@ -5972,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="Q37" t="n">
         <v>9</v>
@@ -5981,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="38">
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -6021,7 +6021,7 @@
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="M38" t="n">
         <v>1</v>
@@ -6033,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="Q38" t="n">
         <v>9</v>
@@ -6042,7 +6042,7 @@
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="39">
@@ -6052,40 +6052,40 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="C39" t="n">
-        <v>0.968203</v>
+        <v>0.970935</v>
       </c>
       <c r="D39" t="n">
-        <v>0.116923</v>
+        <v>0.11129</v>
       </c>
       <c r="E39" t="n">
-        <v>0.003095</v>
+        <v>0.002319</v>
       </c>
       <c r="F39" t="n">
-        <v>0.962136</v>
+        <v>0.9663890000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9742690000000001</v>
+        <v>0.97548</v>
       </c>
       <c r="H39" t="n">
-        <v>0.971268</v>
+        <v>0.974164</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9653119999999999</v>
+        <v>0.969388</v>
       </c>
       <c r="J39" t="n">
-        <v>0.977225</v>
+        <v>0.978723</v>
       </c>
       <c r="K39" t="n">
-        <v>0.942537</v>
+        <v>0.9483279999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9292319999999999</v>
+        <v>0.938518</v>
       </c>
       <c r="M39" t="n">
-        <v>0.953466</v>
+        <v>0.956646</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -6094,16 +6094,16 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="Q39" t="n">
         <v>9</v>
       </c>
       <c r="R39" t="n">
-        <v>0.943111</v>
+        <v>0.948844</v>
       </c>
       <c r="S39" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="40">
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="C40" t="n">
         <v>0.5</v>
@@ -6146,7 +6146,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -6155,16 +6155,16 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="Q40" t="n">
         <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="S40" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="42">
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -9185,7 +9185,7 @@
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -9197,7 +9197,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="Q31" t="n">
         <v>9</v>
@@ -9206,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="32">
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -9246,7 +9246,7 @@
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
@@ -9258,7 +9258,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="Q32" t="n">
         <v>9</v>
@@ -9267,7 +9267,7 @@
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="33">
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="C33" t="n">
         <v>0.5</v>
@@ -9295,13 +9295,13 @@
         <v>0.5</v>
       </c>
       <c r="H33" t="n">
-        <v>0.50025</v>
+        <v>0.5</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.499444</v>
       </c>
       <c r="J33" t="n">
-        <v>0.50075</v>
+        <v>0.500556</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -9310,25 +9310,25 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>0.00037</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>6.499999999999999e-05</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001917</v>
+        <v>0.002095</v>
       </c>
       <c r="Q33" t="n">
         <v>9</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="S33" t="n">
-        <v>0.009995</v>
+        <v>0.010352</v>
       </c>
     </row>
     <row r="34">
@@ -9338,40 +9338,40 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="C34" t="n">
-        <v>0.999125</v>
+        <v>0.998634</v>
       </c>
       <c r="D34" t="n">
-        <v>0.01338</v>
+        <v>0.01847</v>
       </c>
       <c r="E34" t="n">
-        <v>0.000299</v>
+        <v>0.000355</v>
       </c>
       <c r="F34" t="n">
-        <v>0.998539</v>
+        <v>0.997938</v>
       </c>
       <c r="G34" t="n">
-        <v>0.999711</v>
+        <v>0.999331</v>
       </c>
       <c r="H34" t="n">
-        <v>0.99975</v>
+        <v>0.999444</v>
       </c>
       <c r="I34" t="n">
-        <v>0.99925</v>
+        <v>0.998704</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.998889</v>
       </c>
       <c r="L34" t="n">
-        <v>0.997173</v>
+        <v>0.996738</v>
       </c>
       <c r="M34" t="n">
-        <v>0.999912</v>
+        <v>0.999622</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -9380,16 +9380,16 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="Q34" t="n">
         <v>9</v>
       </c>
       <c r="R34" t="n">
-        <v>0.999505</v>
+        <v>0.9989</v>
       </c>
       <c r="S34" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="35">
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -9429,7 +9429,7 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>
@@ -9441,7 +9441,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="Q35" t="n">
         <v>9</v>
@@ -9450,7 +9450,7 @@
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="36">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -9490,7 +9490,7 @@
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="M36" t="n">
         <v>1</v>
@@ -9502,7 +9502,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="Q36" t="n">
         <v>9</v>
@@ -9511,7 +9511,7 @@
         <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="37">
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -9551,7 +9551,7 @@
         <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="M37" t="n">
         <v>1</v>
@@ -9563,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="Q37" t="n">
         <v>9</v>
@@ -9572,7 +9572,7 @@
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="38">
@@ -9582,7 +9582,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -9612,7 +9612,7 @@
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="M38" t="n">
         <v>1</v>
@@ -9624,7 +9624,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="Q38" t="n">
         <v>9</v>
@@ -9633,7 +9633,7 @@
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="39">
@@ -9643,40 +9643,40 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="C39" t="n">
-        <v>0.999031</v>
+        <v>0.999051</v>
       </c>
       <c r="D39" t="n">
-        <v>0.016688</v>
+        <v>0.017366</v>
       </c>
       <c r="E39" t="n">
-        <v>0.000373</v>
+        <v>0.000334</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9983</v>
+        <v>0.998396</v>
       </c>
       <c r="G39" t="n">
-        <v>0.999763</v>
+        <v>0.999706</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.999444</v>
       </c>
       <c r="I39" t="n">
-        <v>0.99875</v>
+        <v>0.998704</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0.999</v>
+        <v>0.998889</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9963610000000001</v>
+        <v>0.996738</v>
       </c>
       <c r="M39" t="n">
-        <v>0.999726</v>
+        <v>0.999622</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -9685,16 +9685,16 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="Q39" t="n">
         <v>9</v>
       </c>
       <c r="R39" t="n">
-        <v>0.99901</v>
+        <v>0.9989</v>
       </c>
       <c r="S39" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="40">
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="C40" t="n">
         <v>0.5</v>
@@ -9737,7 +9737,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -9746,16 +9746,16 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="Q40" t="n">
         <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="S40" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="42">
@@ -12797,7 +12797,7 @@
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="32">
@@ -12858,7 +12858,7 @@
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="33">
@@ -12916,10 +12916,10 @@
         <v>9</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="S33" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="34">
@@ -12980,7 +12980,7 @@
         <v>0.99939</v>
       </c>
       <c r="S34" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="35">
@@ -13041,7 +13041,7 @@
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="36">
@@ -13102,7 +13102,7 @@
         <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="37">
@@ -13163,7 +13163,7 @@
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="38">
@@ -13224,7 +13224,7 @@
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="39">
@@ -13282,10 +13282,10 @@
         <v>9</v>
       </c>
       <c r="R39" t="n">
-        <v>0.958496</v>
+        <v>0.958495</v>
       </c>
       <c r="S39" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="40">
@@ -13343,10 +13343,10 @@
         <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="S40" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="42">
@@ -16388,7 +16388,7 @@
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="32">
@@ -16449,7 +16449,7 @@
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="33">
@@ -16507,10 +16507,10 @@
         <v>9</v>
       </c>
       <c r="R33" t="n">
-        <v>0.010495</v>
+        <v>0.010484</v>
       </c>
       <c r="S33" t="n">
-        <v>0.009995</v>
+        <v>0.009984</v>
       </c>
     </row>
     <row r="34">
@@ -16571,7 +16571,7 @@
         <v>0.999505</v>
       </c>
       <c r="S34" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="35">
@@ -16632,7 +16632,7 @@
         <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="36">
@@ -16693,7 +16693,7 @@
         <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="37">
@@ -16754,7 +16754,7 @@
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="38">
@@ -16815,7 +16815,7 @@
         <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="39">
@@ -16873,10 +16873,10 @@
         <v>9</v>
       </c>
       <c r="R39" t="n">
-        <v>0.940105</v>
+        <v>0.9401040000000001</v>
       </c>
       <c r="S39" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="40">
@@ -16934,10 +16934,10 @@
         <v>9</v>
       </c>
       <c r="R40" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="S40" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="42">
@@ -18493,10 +18493,10 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>70490</v>
+        <v>86250</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.2e-05</v>
       </c>
       <c r="F4" t="n">
         <v>0.01</v>
@@ -18505,7 +18505,7 @@
         <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="5">
@@ -25364,7 +25364,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -25394,7 +25394,7 @@
         <v>1</v>
       </c>
       <c r="N82" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="O82" t="n">
         <v>1</v>
@@ -25406,7 +25406,7 @@
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="S82" t="n">
         <v>9</v>
@@ -25415,7 +25415,7 @@
         <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="83">
@@ -25435,7 +25435,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -25465,7 +25465,7 @@
         <v>1</v>
       </c>
       <c r="N83" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="O83" t="n">
         <v>1</v>
@@ -25477,7 +25477,7 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="S83" t="n">
         <v>9</v>
@@ -25486,7 +25486,7 @@
         <v>1</v>
       </c>
       <c r="U83" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="84">
@@ -25506,40 +25506,40 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="E84" t="n">
-        <v>0.500613</v>
+        <v>0.500733</v>
       </c>
       <c r="F84" t="n">
-        <v>0.015336</v>
+        <v>0.017217</v>
       </c>
       <c r="G84" t="n">
-        <v>0.000406</v>
+        <v>0.000359</v>
       </c>
       <c r="H84" t="n">
-        <v>0.499817</v>
+        <v>0.50003</v>
       </c>
       <c r="I84" t="n">
-        <v>0.501409</v>
+        <v>0.501436</v>
       </c>
       <c r="J84" t="n">
-        <v>0.501051</v>
+        <v>0.501086</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5</v>
+        <v>0.500217</v>
       </c>
       <c r="L84" t="n">
-        <v>0.502453</v>
+        <v>0.502171</v>
       </c>
       <c r="M84" t="n">
-        <v>0.002102</v>
+        <v>0.002171</v>
       </c>
       <c r="N84" t="n">
-        <v>0.000715</v>
+        <v>0.000928</v>
       </c>
       <c r="O84" t="n">
-        <v>0.006163</v>
+        <v>0.005072</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -25548,16 +25548,16 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="S84" t="n">
         <v>9</v>
       </c>
       <c r="T84" t="n">
-        <v>0.012082</v>
+        <v>0.012138</v>
       </c>
       <c r="U84" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="85">
@@ -25577,22 +25577,22 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="E85" t="n">
-        <v>0.99965</v>
+        <v>0.99962</v>
       </c>
       <c r="F85" t="n">
-        <v>0.005222</v>
+        <v>0.005197</v>
       </c>
       <c r="G85" t="n">
-        <v>0.000138</v>
+        <v>0.000108</v>
       </c>
       <c r="H85" t="n">
-        <v>0.999379</v>
+        <v>0.999408</v>
       </c>
       <c r="I85" t="n">
-        <v>0.9999209999999999</v>
+        <v>0.9998320000000001</v>
       </c>
       <c r="J85" t="n">
         <v>1</v>
@@ -25607,7 +25607,7 @@
         <v>1</v>
       </c>
       <c r="N85" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
@@ -25619,7 +25619,7 @@
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="S85" t="n">
         <v>9</v>
@@ -25628,7 +25628,7 @@
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="86">
@@ -25648,7 +25648,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -25678,7 +25678,7 @@
         <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="O86" t="n">
         <v>1</v>
@@ -25690,7 +25690,7 @@
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="S86" t="n">
         <v>9</v>
@@ -25699,7 +25699,7 @@
         <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="87">
@@ -25719,7 +25719,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -25749,7 +25749,7 @@
         <v>1</v>
       </c>
       <c r="N87" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="O87" t="n">
         <v>1</v>
@@ -25761,7 +25761,7 @@
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="S87" t="n">
         <v>9</v>
@@ -25770,7 +25770,7 @@
         <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="88">
@@ -25790,7 +25790,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -25820,7 +25820,7 @@
         <v>1</v>
       </c>
       <c r="N88" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="O88" t="n">
         <v>1</v>
@@ -25832,7 +25832,7 @@
         <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="S88" t="n">
         <v>9</v>
@@ -25841,7 +25841,7 @@
         <v>1</v>
       </c>
       <c r="U88" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="89">
@@ -25861,7 +25861,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -25891,7 +25891,7 @@
         <v>1</v>
       </c>
       <c r="N89" t="n">
-        <v>0.997315</v>
+        <v>0.998335</v>
       </c>
       <c r="O89" t="n">
         <v>1</v>
@@ -25903,7 +25903,7 @@
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="S89" t="n">
         <v>9</v>
@@ -25912,7 +25912,7 @@
         <v>1</v>
       </c>
       <c r="U89" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="90">
@@ -25932,40 +25932,40 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="E90" t="n">
-        <v>0.968203</v>
+        <v>0.970935</v>
       </c>
       <c r="F90" t="n">
-        <v>0.116923</v>
+        <v>0.11129</v>
       </c>
       <c r="G90" t="n">
-        <v>0.003095</v>
+        <v>0.002319</v>
       </c>
       <c r="H90" t="n">
-        <v>0.962136</v>
+        <v>0.9663890000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>0.9742690000000001</v>
+        <v>0.97548</v>
       </c>
       <c r="J90" t="n">
-        <v>0.971268</v>
+        <v>0.974164</v>
       </c>
       <c r="K90" t="n">
-        <v>0.9653119999999999</v>
+        <v>0.969388</v>
       </c>
       <c r="L90" t="n">
-        <v>0.977225</v>
+        <v>0.978723</v>
       </c>
       <c r="M90" t="n">
-        <v>0.942537</v>
+        <v>0.9483279999999999</v>
       </c>
       <c r="N90" t="n">
-        <v>0.9292319999999999</v>
+        <v>0.938518</v>
       </c>
       <c r="O90" t="n">
-        <v>0.953466</v>
+        <v>0.956646</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -25974,16 +25974,16 @@
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="S90" t="n">
         <v>9</v>
       </c>
       <c r="T90" t="n">
-        <v>0.943111</v>
+        <v>0.948844</v>
       </c>
       <c r="U90" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="91">
@@ -26003,7 +26003,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1427</v>
+        <v>2303</v>
       </c>
       <c r="E91" t="n">
         <v>0.5</v>
@@ -26036,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -26045,16 +26045,16 @@
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0.002685</v>
+        <v>0.001665</v>
       </c>
       <c r="S91" t="n">
         <v>9</v>
       </c>
       <c r="T91" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="U91" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="92">
@@ -26074,7 +26074,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -26104,7 +26104,7 @@
         <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="O92" t="n">
         <v>1</v>
@@ -26116,7 +26116,7 @@
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="S92" t="n">
         <v>9</v>
@@ -26125,7 +26125,7 @@
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="93">
@@ -26145,7 +26145,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -26175,7 +26175,7 @@
         <v>1</v>
       </c>
       <c r="N93" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
@@ -26187,7 +26187,7 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="S93" t="n">
         <v>9</v>
@@ -26196,7 +26196,7 @@
         <v>1</v>
       </c>
       <c r="U93" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="94">
@@ -26216,7 +26216,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E94" t="n">
         <v>0.5</v>
@@ -26234,13 +26234,13 @@
         <v>0.5</v>
       </c>
       <c r="J94" t="n">
-        <v>0.50025</v>
+        <v>0.5</v>
       </c>
       <c r="K94" t="n">
-        <v>0.5</v>
+        <v>0.499444</v>
       </c>
       <c r="L94" t="n">
-        <v>0.50075</v>
+        <v>0.500556</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -26249,25 +26249,25 @@
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>0.00037</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>6.499999999999999e-05</v>
       </c>
       <c r="R94" t="n">
-        <v>0.001917</v>
+        <v>0.002095</v>
       </c>
       <c r="S94" t="n">
         <v>9</v>
       </c>
       <c r="T94" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="U94" t="n">
-        <v>0.009995</v>
+        <v>0.010352</v>
       </c>
     </row>
     <row r="95">
@@ -26287,40 +26287,40 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E95" t="n">
-        <v>0.999125</v>
+        <v>0.998634</v>
       </c>
       <c r="F95" t="n">
-        <v>0.01338</v>
+        <v>0.01847</v>
       </c>
       <c r="G95" t="n">
-        <v>0.000299</v>
+        <v>0.000355</v>
       </c>
       <c r="H95" t="n">
-        <v>0.998539</v>
+        <v>0.997938</v>
       </c>
       <c r="I95" t="n">
-        <v>0.999711</v>
+        <v>0.999331</v>
       </c>
       <c r="J95" t="n">
-        <v>0.99975</v>
+        <v>0.999444</v>
       </c>
       <c r="K95" t="n">
-        <v>0.99925</v>
+        <v>0.998704</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.998889</v>
       </c>
       <c r="N95" t="n">
-        <v>0.997173</v>
+        <v>0.996738</v>
       </c>
       <c r="O95" t="n">
-        <v>0.999912</v>
+        <v>0.999622</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
@@ -26329,16 +26329,16 @@
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="S95" t="n">
         <v>9</v>
       </c>
       <c r="T95" t="n">
-        <v>0.999505</v>
+        <v>0.9989</v>
       </c>
       <c r="U95" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="96">
@@ -26358,7 +26358,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
@@ -26388,7 +26388,7 @@
         <v>1</v>
       </c>
       <c r="N96" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -26400,7 +26400,7 @@
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="S96" t="n">
         <v>9</v>
@@ -26409,7 +26409,7 @@
         <v>1</v>
       </c>
       <c r="U96" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="97">
@@ -26429,7 +26429,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
@@ -26459,7 +26459,7 @@
         <v>1</v>
       </c>
       <c r="N97" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="O97" t="n">
         <v>1</v>
@@ -26471,7 +26471,7 @@
         <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="S97" t="n">
         <v>9</v>
@@ -26480,7 +26480,7 @@
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="98">
@@ -26500,7 +26500,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E98" t="n">
         <v>1</v>
@@ -26530,7 +26530,7 @@
         <v>1</v>
       </c>
       <c r="N98" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="O98" t="n">
         <v>1</v>
@@ -26542,7 +26542,7 @@
         <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="S98" t="n">
         <v>9</v>
@@ -26551,7 +26551,7 @@
         <v>1</v>
       </c>
       <c r="U98" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="99">
@@ -26571,7 +26571,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E99" t="n">
         <v>1</v>
@@ -26601,7 +26601,7 @@
         <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>0.9980830000000001</v>
+        <v>0.998579</v>
       </c>
       <c r="O99" t="n">
         <v>1</v>
@@ -26613,7 +26613,7 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="S99" t="n">
         <v>9</v>
@@ -26622,7 +26622,7 @@
         <v>1</v>
       </c>
       <c r="U99" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="100">
@@ -26642,40 +26642,40 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E100" t="n">
-        <v>0.999031</v>
+        <v>0.999051</v>
       </c>
       <c r="F100" t="n">
-        <v>0.016688</v>
+        <v>0.017366</v>
       </c>
       <c r="G100" t="n">
-        <v>0.000373</v>
+        <v>0.000334</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9983</v>
+        <v>0.998396</v>
       </c>
       <c r="I100" t="n">
-        <v>0.999763</v>
+        <v>0.999706</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.999444</v>
       </c>
       <c r="K100" t="n">
-        <v>0.99875</v>
+        <v>0.998704</v>
       </c>
       <c r="L100" t="n">
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>0.999</v>
+        <v>0.998889</v>
       </c>
       <c r="N100" t="n">
-        <v>0.9963610000000001</v>
+        <v>0.996738</v>
       </c>
       <c r="O100" t="n">
-        <v>0.999726</v>
+        <v>0.999622</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
@@ -26684,16 +26684,16 @@
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="S100" t="n">
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>0.99901</v>
+        <v>0.9989</v>
       </c>
       <c r="U100" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="101">
@@ -26713,7 +26713,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2000</v>
+        <v>2700</v>
       </c>
       <c r="E101" t="n">
         <v>0.5</v>
@@ -26746,7 +26746,7 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="P101" t="n">
         <v>0</v>
@@ -26755,16 +26755,16 @@
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0.001917</v>
+        <v>0.001421</v>
       </c>
       <c r="S101" t="n">
         <v>9</v>
       </c>
       <c r="T101" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="U101" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="102">
@@ -26835,7 +26835,7 @@
         <v>1</v>
       </c>
       <c r="U102" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="103">
@@ -26906,7 +26906,7 @@
         <v>1</v>
       </c>
       <c r="U103" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="104">
@@ -26974,10 +26974,10 @@
         <v>9</v>
       </c>
       <c r="T104" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="U104" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="105">
@@ -27048,7 +27048,7 @@
         <v>0.99939</v>
       </c>
       <c r="U105" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="106">
@@ -27119,7 +27119,7 @@
         <v>1</v>
       </c>
       <c r="U106" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="107">
@@ -27190,7 +27190,7 @@
         <v>1</v>
       </c>
       <c r="U107" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="108">
@@ -27261,7 +27261,7 @@
         <v>1</v>
       </c>
       <c r="U108" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="109">
@@ -27332,7 +27332,7 @@
         <v>1</v>
       </c>
       <c r="U109" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="110">
@@ -27400,10 +27400,10 @@
         <v>9</v>
       </c>
       <c r="T110" t="n">
-        <v>0.958496</v>
+        <v>0.958495</v>
       </c>
       <c r="U110" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="111">
@@ -27471,10 +27471,10 @@
         <v>9</v>
       </c>
       <c r="T111" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="U111" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="112">
@@ -27545,7 +27545,7 @@
         <v>1</v>
       </c>
       <c r="U112" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="113">
@@ -27616,7 +27616,7 @@
         <v>1</v>
       </c>
       <c r="U113" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="114">
@@ -27684,10 +27684,10 @@
         <v>9</v>
       </c>
       <c r="T114" t="n">
-        <v>0.010495</v>
+        <v>0.010484</v>
       </c>
       <c r="U114" t="n">
-        <v>0.009995</v>
+        <v>0.009984</v>
       </c>
     </row>
     <row r="115">
@@ -27758,7 +27758,7 @@
         <v>0.999505</v>
       </c>
       <c r="U115" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="116">
@@ -27829,7 +27829,7 @@
         <v>1</v>
       </c>
       <c r="U116" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="117">
@@ -27900,7 +27900,7 @@
         <v>1</v>
       </c>
       <c r="U117" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="118">
@@ -27971,7 +27971,7 @@
         <v>1</v>
       </c>
       <c r="U118" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="119">
@@ -28042,7 +28042,7 @@
         <v>1</v>
       </c>
       <c r="U119" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="120">
@@ -28110,10 +28110,10 @@
         <v>9</v>
       </c>
       <c r="T120" t="n">
-        <v>0.940105</v>
+        <v>0.9401040000000001</v>
       </c>
       <c r="U120" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="121">
@@ -28181,10 +28181,10 @@
         <v>9</v>
       </c>
       <c r="T121" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
       <c r="U121" t="n">
-        <v>0.01</v>
+        <v>0.009989</v>
       </c>
     </row>
     <row r="122">
